--- a/wyniki/miasta_2019_wiecej_niz_100k.xlsx
+++ b/wyniki/miasta_2019_wiecej_niz_100k.xlsx
@@ -541,16 +541,16 @@
         <v>0.9276301048202865</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4856363070792466</v>
+        <v>2.718469715577259</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6408382169089795</v>
+        <v>2.039881173139117</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2631491278953909</v>
+        <v>1.919835693296355</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9276301048202865</v>
+        <v>2.594088763229158</v>
       </c>
     </row>
     <row r="3">
@@ -596,16 +596,16 @@
         <v>0.9083272298548372</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4076304784664999</v>
+        <v>2.9220772297967</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4626483755625396</v>
+        <v>1.842704915238949</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3289773597409859</v>
+        <v>1.968316552696053</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9083272298548372</v>
+        <v>2.624381211512792</v>
       </c>
     </row>
     <row r="4">
@@ -651,16 +651,16 @@
         <v>1.239892063348117</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.734944678522368</v>
+        <v>5.956965055626686</v>
       </c>
       <c r="O4" t="n">
-        <v>1.029837802091079</v>
+        <v>2.590216298128995</v>
       </c>
       <c r="P4" t="n">
-        <v>1.023499196573527</v>
+        <v>2.710832824209072</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.239892063348117</v>
+        <v>3.592562581921396</v>
       </c>
     </row>
     <row r="5">
@@ -706,16 +706,16 @@
         <v>1.244578075055676</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.779364949429205</v>
+        <v>6.12355306998786</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9413780272658201</v>
+        <v>2.408889260560331</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09001024562779</v>
+        <v>2.96969884398889</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.244578075055676</v>
+        <v>3.461152797060065</v>
       </c>
     </row>
     <row r="6">
@@ -761,16 +761,16 @@
         <v>1.258472670261645</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.738781177600544</v>
+        <v>5.984094009253067</v>
       </c>
       <c r="O6" t="n">
-        <v>1.065326585586881</v>
+        <v>2.667881324071519</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9868969311261553</v>
+        <v>2.537622696779478</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.258472670261645</v>
+        <v>3.627690767892659</v>
       </c>
     </row>
     <row r="7">
@@ -816,16 +816,16 @@
         <v>1.173002335706206</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.783481017881196</v>
+        <v>6.115185639126209</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8793862499226665</v>
+        <v>2.39661917620032</v>
       </c>
       <c r="P7" t="n">
-        <v>1.143974464569284</v>
+        <v>3.158987539621235</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.173002335706206</v>
+        <v>3.424929764115211</v>
       </c>
     </row>
     <row r="8">
@@ -871,16 +871,16 @@
         <v>1.586025105818297</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9183973058292112</v>
+        <v>3.102811364887112</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9094084813895865</v>
+        <v>3.021938365273526</v>
       </c>
       <c r="P8" t="n">
-        <v>1.034883277960795</v>
+        <v>3.631565250044704</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.586025105818297</v>
+        <v>5.728809552946637</v>
       </c>
     </row>
     <row r="9">
@@ -926,16 +926,16 @@
         <v>1.569416739381229</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3833885520048805</v>
+        <v>2.829778014364788</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9137060008797153</v>
+        <v>2.849111595769911</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9807706293162873</v>
+        <v>3.321771870749344</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.569416739381229</v>
+        <v>5.541657602853281</v>
       </c>
     </row>
     <row r="10">
@@ -981,16 +981,16 @@
         <v>0.7890069014309472</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8395395101891079</v>
+        <v>3.699071530506034</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9611852248284989</v>
+        <v>3.162934894334926</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5591910057963498</v>
+        <v>2.131917091775028</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7890069014309472</v>
+        <v>2.862975072174287</v>
       </c>
     </row>
     <row r="11">
@@ -1036,16 +1036,16 @@
         <v>1.217393721355659</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5444796954072588</v>
+        <v>2.207993577358276</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2476294304100511</v>
+        <v>1.806791378066047</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04398754941050283</v>
+        <v>2.104289871187421</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.217393721355659</v>
+        <v>4.253757087613171</v>
       </c>
     </row>
     <row r="12">
@@ -1091,16 +1091,16 @@
         <v>0.712450729350131</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3615677029832018</v>
+        <v>2.52806377340908</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4064598647628084</v>
+        <v>3.320434895909604</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0125374861197467</v>
+        <v>1.819877788108656</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.712450729350131</v>
+        <v>2.232443997505202</v>
       </c>
     </row>
     <row r="13">
@@ -1146,16 +1146,16 @@
         <v>1.675693976612972</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7520222511369603</v>
+        <v>3.045106632411503</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8521228134100971</v>
+        <v>2.600184906870096</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9668771441438233</v>
+        <v>3.16291901656058</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.675693976612972</v>
+        <v>5.786654817856753</v>
       </c>
     </row>
     <row r="14">
@@ -1201,16 +1201,16 @@
         <v>1.352290025453697</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7954358367897357</v>
+        <v>3.57873695383284</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.04902796930857579</v>
+        <v>1.433542061761846</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0359918596813859</v>
+        <v>1.619327580067891</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.352290025453697</v>
+        <v>4.222044894935304</v>
       </c>
     </row>
     <row r="15">
@@ -1256,16 +1256,16 @@
         <v>1.62485561829778</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8064264117854256</v>
+        <v>2.577849477702007</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1724885400685691</v>
+        <v>1.707480449402121</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0531465122583015</v>
+        <v>1.719780772519462</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.62485561829778</v>
+        <v>5.634207549717075</v>
       </c>
     </row>
     <row r="16">
@@ -1311,16 +1311,16 @@
         <v>0.3527934620505457</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4967259180511873</v>
+        <v>1.833626344543178</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7004713005951773</v>
+        <v>3.931857294966982</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2935347169171658</v>
+        <v>2.573940079619976</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3527934620505457</v>
+        <v>2.882137894317518</v>
       </c>
     </row>
     <row r="17">
@@ -1366,16 +1366,16 @@
         <v>0.2363285672538041</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4480891062019849</v>
+        <v>2.563748511818045</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6710629756143003</v>
+        <v>2.498276873201097</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792990207921787</v>
+        <v>2.356153319877287</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2363285672538041</v>
+        <v>2.429523128310891</v>
       </c>
     </row>
     <row r="18">
@@ -1421,16 +1421,16 @@
         <v>0.5486095308326717</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.004484964427357</v>
+        <v>3.541538296917753</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4672142268430448</v>
+        <v>1.506183118288876</v>
       </c>
       <c r="P18" t="n">
-        <v>0.706232678754691</v>
+        <v>2.251172339738153</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5486095308326717</v>
+        <v>2.220733187911779</v>
       </c>
     </row>
     <row r="19">
@@ -1476,16 +1476,16 @@
         <v>0.4676490910673179</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.954667682087938</v>
+        <v>3.420652988106816</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6264515086098991</v>
+        <v>2.092597529582122</v>
       </c>
       <c r="P19" t="n">
-        <v>1.058942783150952</v>
+        <v>3.369474121725987</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4676490910673179</v>
+        <v>2.115690632266731</v>
       </c>
     </row>
     <row r="20">
@@ -1531,16 +1531,16 @@
         <v>0.2263869136387036</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.782783185441335</v>
+        <v>5.963653384784547</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8943710694471526</v>
+        <v>2.275227861186184</v>
       </c>
       <c r="P20" t="n">
-        <v>1.073710830576893</v>
+        <v>3.323732089368514</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2263869136387036</v>
+        <v>1.917999865321145</v>
       </c>
     </row>
     <row r="21">
@@ -1586,16 +1586,16 @@
         <v>0.4157400294319445</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.783793487855061</v>
+        <v>5.887133928411846</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8735153936800357</v>
+        <v>2.305675302570712</v>
       </c>
       <c r="P21" t="n">
-        <v>1.109882848502488</v>
+        <v>3.514774537025627</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4157400294319445</v>
+        <v>2.498068612094219</v>
       </c>
     </row>
     <row r="22">
@@ -1641,16 +1641,16 @@
         <v>0.4148222132318721</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.873044755797407</v>
+        <v>6.142246485138476</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8537487151655789</v>
+        <v>2.244580325663402</v>
       </c>
       <c r="P22" t="n">
-        <v>1.067408408144501</v>
+        <v>3.372690295319666</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4148222132318721</v>
+        <v>2.382946456064771</v>
       </c>
     </row>
     <row r="23">
@@ -1696,16 +1696,16 @@
         <v>0.4748046538843147</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.871715826977334</v>
+        <v>6.132968370735847</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8422035303334704</v>
+        <v>2.281032035924187</v>
       </c>
       <c r="P23" t="n">
-        <v>1.160352995883938</v>
+        <v>3.687058706692304</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4748046538843147</v>
+        <v>2.593062572442314</v>
       </c>
     </row>
     <row r="24">
@@ -1751,16 +1751,16 @@
         <v>1.538116151773415</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5351717629765366</v>
+        <v>1.927061892979317</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7812810653537654</v>
+        <v>3.755191051840296</v>
       </c>
       <c r="P24" t="n">
-        <v>1.057172878020129</v>
+        <v>3.461914042878517</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.538116151773415</v>
+        <v>4.905998137980451</v>
       </c>
     </row>
     <row r="25">
@@ -1806,16 +1806,16 @@
         <v>1.469170302120613</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5357051264202023</v>
+        <v>1.92707582834126</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6922426302904753</v>
+        <v>3.472337109669916</v>
       </c>
       <c r="P25" t="n">
-        <v>1.032615057957172</v>
+        <v>3.424500312198842</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.469170302120613</v>
+        <v>4.732302814066387</v>
       </c>
     </row>
     <row r="26">
@@ -1861,16 +1861,16 @@
         <v>1.432390881871453</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5431212181526186</v>
+        <v>1.940530471029879</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7971637045539409</v>
+        <v>3.550233863268026</v>
       </c>
       <c r="P26" t="n">
-        <v>1.002185915145185</v>
+        <v>3.110793588454368</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.432390881871453</v>
+        <v>4.693464920762255</v>
       </c>
     </row>
     <row r="27">
@@ -1916,16 +1916,16 @@
         <v>1.140676116224962</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5388018940752719</v>
+        <v>1.933783425760295</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7519656194909897</v>
+        <v>3.258451668067631</v>
       </c>
       <c r="P27" t="n">
-        <v>0.993336717867774</v>
+        <v>3.038331589365898</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.140676116224962</v>
+        <v>4.015094176246178</v>
       </c>
     </row>
     <row r="28">
@@ -1971,16 +1971,16 @@
         <v>1.619161962666648</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5361208164720466</v>
+        <v>1.93353718660219</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8063690702341223</v>
+        <v>3.921854545604964</v>
       </c>
       <c r="P28" t="n">
-        <v>1.04447715124838</v>
+        <v>3.430270887284012</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.619161962666648</v>
+        <v>5.237088458197601</v>
       </c>
     </row>
     <row r="29">
@@ -2026,16 +2026,16 @@
         <v>0.2718978321759021</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5471770771871822</v>
+        <v>1.943481845796242</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5898466489090682</v>
+        <v>2.546436771154654</v>
       </c>
       <c r="P29" t="n">
-        <v>0.899094973032843</v>
+        <v>2.755041007817022</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2718978321759021</v>
+        <v>2.317030630948337</v>
       </c>
     </row>
     <row r="30">
@@ -2081,16 +2081,16 @@
         <v>0.2261512574139023</v>
       </c>
       <c r="N30" t="n">
-        <v>0.547711677015183</v>
+        <v>1.943511378211482</v>
       </c>
       <c r="O30" t="n">
-        <v>0.544148098607235</v>
+        <v>2.498363529586797</v>
       </c>
       <c r="P30" t="n">
-        <v>0.881123507394118</v>
+        <v>2.726860525019685</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2261512574139023</v>
+        <v>2.189116302823913</v>
       </c>
     </row>
     <row r="31">
@@ -2136,16 +2136,16 @@
         <v>0.4228598230499327</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5479412035206866</v>
+        <v>1.944382481559155</v>
       </c>
       <c r="O31" t="n">
-        <v>0.694645166506326</v>
+        <v>2.912016394890494</v>
       </c>
       <c r="P31" t="n">
-        <v>0.9253916104419975</v>
+        <v>2.857492271455337</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4228598230499327</v>
+        <v>2.622790861629259</v>
       </c>
     </row>
     <row r="32">
@@ -2191,16 +2191,16 @@
         <v>0.1359872200279492</v>
       </c>
       <c r="N32" t="n">
-        <v>0.5479460342159997</v>
+        <v>1.942656412639516</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5865733306606739</v>
+        <v>2.348451291748184</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8931017089438954</v>
+        <v>2.701006013052554</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1359872200279492</v>
+        <v>2.002701880014463</v>
       </c>
     </row>
     <row r="33">
@@ -2246,16 +2246,16 @@
         <v>0.4784301250951626</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5357960651462017</v>
+        <v>1.922223374969472</v>
       </c>
       <c r="O33" t="n">
-        <v>0.75590164857261</v>
+        <v>2.766961497711043</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9289294586651277</v>
+        <v>2.767993113619514</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4784301250951626</v>
+        <v>2.982769184137589</v>
       </c>
     </row>
     <row r="34">
@@ -2301,16 +2301,16 @@
         <v>0.3944071833573765</v>
       </c>
       <c r="N34" t="n">
-        <v>0.535223032479059</v>
+        <v>1.921415553565015</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7125715509149367</v>
+        <v>2.685686380679727</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9192264558819369</v>
+        <v>2.764680267683306</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3944071833573765</v>
+        <v>2.74000797189164</v>
       </c>
     </row>
     <row r="35">
@@ -2356,16 +2356,16 @@
         <v>0.4973536741769137</v>
       </c>
       <c r="N35" t="n">
-        <v>0.3493045670998122</v>
+        <v>1.546898826456354</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8717628641096535</v>
+        <v>2.983745391747165</v>
       </c>
       <c r="P35" t="n">
-        <v>1.062322530846519</v>
+        <v>2.922325106534614</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4973536741769137</v>
+        <v>2.5334023069145</v>
       </c>
     </row>
     <row r="36">
@@ -2411,16 +2411,16 @@
         <v>0.5205292633340577</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.108017036618507</v>
+        <v>2.528988238705951</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1616100552930694</v>
+        <v>1.725796705706794</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4793578458427966</v>
+        <v>1.715774137962061</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5205292633340577</v>
+        <v>2.770464629766652</v>
       </c>
     </row>
     <row r="37">
@@ -2466,16 +2466,16 @@
         <v>0.02658367094204747</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.03946428186310656</v>
+        <v>2.42074567466036</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.3316423268598184</v>
+        <v>1.749012256596632</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.1594243042625422</v>
+        <v>1.510223595593253</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.02658367094204747</v>
+        <v>1.441285073426715</v>
       </c>
     </row>
     <row r="38">
@@ -2521,16 +2521,16 @@
         <v>1.911954399409065</v>
       </c>
       <c r="N38" t="n">
-        <v>0.1412826944889614</v>
+        <v>3.078069307317624</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9222017877681296</v>
+        <v>2.859558691494248</v>
       </c>
       <c r="P38" t="n">
-        <v>0.965733915730556</v>
+        <v>3.16461556362407</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.911954399409065</v>
+        <v>6.678920736186872</v>
       </c>
     </row>
     <row r="39">
@@ -2576,16 +2576,16 @@
         <v>0.4389540848274203</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.6653399816757797</v>
+        <v>2.5034058581011</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6548142044918397</v>
+        <v>2.183929201188982</v>
       </c>
       <c r="P39" t="n">
-        <v>1.070115308499887</v>
+        <v>3.370669506530566</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4389540848274203</v>
+        <v>2.728479563960182</v>
       </c>
     </row>
     <row r="40">
@@ -2631,16 +2631,16 @@
         <v>0.1475080831400344</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.347321621123685</v>
+        <v>4.214896361858558</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4574341918331626</v>
+        <v>1.786615850009991</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7818027373701971</v>
+        <v>3.08168483455922</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1475080831400344</v>
+        <v>2.199502590165311</v>
       </c>
     </row>
     <row r="41">
@@ -2686,16 +2686,16 @@
         <v>0.1384585574941647</v>
       </c>
       <c r="N41" t="n">
-        <v>-1.348219902587992</v>
+        <v>4.216031779352798</v>
       </c>
       <c r="O41" t="n">
-        <v>0.4377891155666704</v>
+        <v>1.796874961224473</v>
       </c>
       <c r="P41" t="n">
-        <v>0.7741013959620501</v>
+        <v>3.047644246257428</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1384585574941647</v>
+        <v>2.226602794207861</v>
       </c>
     </row>
     <row r="42">
@@ -2741,16 +2741,16 @@
         <v>-0.3796792434969676</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.05881064927645903</v>
+        <v>2.650811999340506</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6159968191280605</v>
+        <v>2.556482286023692</v>
       </c>
       <c r="P42" t="n">
-        <v>0.6449807382735853</v>
+        <v>2.642119566624737</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.3796792434969676</v>
+        <v>2.41418760893951</v>
       </c>
     </row>
     <row r="43">
@@ -2796,16 +2796,16 @@
         <v>1.556930868845882</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4775933656096967</v>
+        <v>1.866806482186082</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7154022287415351</v>
+        <v>3.114776836115648</v>
       </c>
       <c r="P43" t="n">
-        <v>1.084647045258713</v>
+        <v>3.681817951274081</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.556930868845882</v>
+        <v>4.879376191778245</v>
       </c>
     </row>
     <row r="44">
@@ -2851,16 +2851,16 @@
         <v>0.8166867473167322</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.1358637388667291</v>
+        <v>1.886495070023114</v>
       </c>
       <c r="O44" t="n">
-        <v>1.078128646571088</v>
+        <v>3.644916599247787</v>
       </c>
       <c r="P44" t="n">
-        <v>1.549518496155844</v>
+        <v>5.489799642482664</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8166867473167322</v>
+        <v>2.743857543817836</v>
       </c>
     </row>
     <row r="45">
@@ -2906,16 +2906,16 @@
         <v>0.2948055170719032</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.6648446762418302</v>
+        <v>2.999368742929067</v>
       </c>
       <c r="O45" t="n">
-        <v>0.6006173860365982</v>
+        <v>3.640757721721588</v>
       </c>
       <c r="P45" t="n">
-        <v>0.4359965615032073</v>
+        <v>3.070390769644272</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2948055170719032</v>
+        <v>2.135629970350148</v>
       </c>
     </row>
     <row r="46">
@@ -2961,16 +2961,16 @@
         <v>0.42457216714294</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.8815444572806316</v>
+        <v>3.537397291829214</v>
       </c>
       <c r="O46" t="n">
-        <v>0.6969025197931928</v>
+        <v>3.637508630512156</v>
       </c>
       <c r="P46" t="n">
-        <v>0.4910476245683727</v>
+        <v>3.179107661547196</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.42457216714294</v>
+        <v>2.618997902242648</v>
       </c>
     </row>
     <row r="47">
@@ -3016,16 +3016,16 @@
         <v>1.238551833539203</v>
       </c>
       <c r="N47" t="n">
-        <v>0.149903027757785</v>
+        <v>2.128401654821682</v>
       </c>
       <c r="O47" t="n">
-        <v>1.112059174338604</v>
+        <v>3.90540443449201</v>
       </c>
       <c r="P47" t="n">
-        <v>1.45331968937138</v>
+        <v>5.053057370156406</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.238551833539203</v>
+        <v>4.49525576717193</v>
       </c>
     </row>
     <row r="48">
@@ -3071,16 +3071,16 @@
         <v>0.9434052912117297</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.4422581916839289</v>
+        <v>2.050149301106583</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8885000377317057</v>
+        <v>2.853674822069691</v>
       </c>
       <c r="P48" t="n">
-        <v>0.4550952284132494</v>
+        <v>2.400653785144296</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9434052912117297</v>
+        <v>3.324949486726289</v>
       </c>
     </row>
     <row r="49">
@@ -3126,16 +3126,16 @@
         <v>1.060826576726482</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02729905338413392</v>
+        <v>2.257159832216968</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.06791858274520846</v>
+        <v>1.548762135129803</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2806013121754998</v>
+        <v>1.926176518816245</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.060826576726482</v>
+        <v>3.477280454622425</v>
       </c>
     </row>
     <row r="50">
@@ -3181,16 +3181,16 @@
         <v>-0.05013947420160955</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.03407295923119978</v>
+        <v>1.674659894730979</v>
       </c>
       <c r="O50" t="n">
-        <v>0.2403839862681267</v>
+        <v>2.372387658322469</v>
       </c>
       <c r="P50" t="n">
-        <v>1.022590365181578</v>
+        <v>4.212732287880804</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.05013947420160955</v>
+        <v>2.349284049251808</v>
       </c>
     </row>
     <row r="51">
@@ -3236,16 +3236,16 @@
         <v>-0.005273553884456965</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.0299145480730522</v>
+        <v>1.670126771921645</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2179938761748493</v>
+        <v>2.300426896740613</v>
       </c>
       <c r="P51" t="n">
-        <v>0.989372967093793</v>
+        <v>4.122967195066721</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.005273553884456965</v>
+        <v>2.417813255739884</v>
       </c>
     </row>
     <row r="52">
@@ -3291,16 +3291,16 @@
         <v>0.7266816018864893</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0944424534569961</v>
+        <v>1.606218662820544</v>
       </c>
       <c r="O52" t="n">
-        <v>1.557720809233696</v>
+        <v>4.93914759090174</v>
       </c>
       <c r="P52" t="n">
-        <v>1.036499219073558</v>
+        <v>3.574011481472232</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.7266816018864893</v>
+        <v>2.993127969941159</v>
       </c>
     </row>
     <row r="53">
@@ -3346,16 +3346,16 @@
         <v>0.8330939081235683</v>
       </c>
       <c r="N53" t="n">
-        <v>0.09862223875325665</v>
+        <v>1.609031023483863</v>
       </c>
       <c r="O53" t="n">
-        <v>1.602026820291079</v>
+        <v>5.056030664115189</v>
       </c>
       <c r="P53" t="n">
-        <v>1.112004234492021</v>
+        <v>3.802174433630359</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.8330939081235683</v>
+        <v>3.17953356584908</v>
       </c>
     </row>
     <row r="54">
@@ -3401,16 +3401,16 @@
         <v>0.7115599536856861</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.2557779125458334</v>
+        <v>2.08575388124365</v>
       </c>
       <c r="O54" t="n">
-        <v>1.429005444048363</v>
+        <v>4.608923503999955</v>
       </c>
       <c r="P54" t="n">
-        <v>0.9610261186905481</v>
+        <v>3.321588175283837</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.7115599536856861</v>
+        <v>3.315674514789015</v>
       </c>
     </row>
     <row r="55">
@@ -3456,16 +3456,16 @@
         <v>0.7835481343423163</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.3523333077617532</v>
+        <v>2.210944932671054</v>
       </c>
       <c r="O55" t="n">
-        <v>1.416551638598129</v>
+        <v>4.524850219393216</v>
       </c>
       <c r="P55" t="n">
-        <v>1.005731618728439</v>
+        <v>3.371394930520822</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.7835481343423163</v>
+        <v>3.555488558433459</v>
       </c>
     </row>
     <row r="56">
@@ -3511,16 +3511,16 @@
         <v>0.6594834118722811</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.3505470618638556</v>
+        <v>2.208611572973875</v>
       </c>
       <c r="O56" t="n">
-        <v>1.472812915061632</v>
+        <v>4.644546860733151</v>
       </c>
       <c r="P56" t="n">
-        <v>1.039338481892797</v>
+        <v>3.440474054574243</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.6594834118722811</v>
+        <v>3.314376864183907</v>
       </c>
     </row>
     <row r="57">
@@ -3566,16 +3566,16 @@
         <v>-0.5223610117472373</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.9789811101512913</v>
+        <v>3.575223393948301</v>
       </c>
       <c r="O57" t="n">
-        <v>0.5942729504735332</v>
+        <v>2.931488711853688</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01661079380753744</v>
+        <v>1.735423460782782</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.5223610117472373</v>
+        <v>2.291742845347576</v>
       </c>
     </row>
     <row r="58">
@@ -3621,16 +3621,16 @@
         <v>0.7628723527315168</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.709681525938354</v>
+        <v>5.949193784563779</v>
       </c>
       <c r="O58" t="n">
-        <v>1.182204218108198</v>
+        <v>3.663751741981957</v>
       </c>
       <c r="P58" t="n">
-        <v>0.8491650991668565</v>
+        <v>3.045348161802901</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.7628723527315168</v>
+        <v>3.508203944863544</v>
       </c>
     </row>
     <row r="59">
@@ -3676,16 +3676,16 @@
         <v>0.825493582894376</v>
       </c>
       <c r="N59" t="n">
-        <v>-1.736038139353844</v>
+        <v>6.016423146758925</v>
       </c>
       <c r="O59" t="n">
-        <v>1.34624648425598</v>
+        <v>4.22016714469393</v>
       </c>
       <c r="P59" t="n">
-        <v>0.9605036956785484</v>
+        <v>3.239256304569895</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.825493582894376</v>
+        <v>3.650287580750086</v>
       </c>
     </row>
     <row r="60">
@@ -3731,16 +3731,16 @@
         <v>0.9082287489276065</v>
       </c>
       <c r="N60" t="n">
-        <v>-1.736038139353844</v>
+        <v>6.016423146758925</v>
       </c>
       <c r="O60" t="n">
-        <v>1.260114971937222</v>
+        <v>3.845085341728411</v>
       </c>
       <c r="P60" t="n">
-        <v>0.9245351956785061</v>
+        <v>3.134096468035216</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.9082287489276065</v>
+        <v>3.735548335834737</v>
       </c>
     </row>
     <row r="61">
@@ -3786,16 +3786,16 @@
         <v>1.25251172185001</v>
       </c>
       <c r="N61" t="n">
-        <v>-2.09532288356064</v>
+        <v>7.062305696681431</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9056916399401056</v>
+        <v>2.831789016161687</v>
       </c>
       <c r="P61" t="n">
-        <v>1.331452581181762</v>
+        <v>4.165216377291684</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.25251172185001</v>
+        <v>4.883353430828442</v>
       </c>
     </row>
     <row r="62">
@@ -3841,16 +3841,16 @@
         <v>0.13067951736961</v>
       </c>
       <c r="N62" t="n">
-        <v>-1.126713405397109</v>
+        <v>4.312829498045486</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4190579694240161</v>
+        <v>2.025248163701732</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3151102531788433</v>
+        <v>1.712201779385127</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.13067951736961</v>
+        <v>1.908603298400486</v>
       </c>
     </row>
     <row r="63">
@@ -3896,16 +3896,16 @@
         <v>0.3370343822289237</v>
       </c>
       <c r="N63" t="n">
-        <v>-0.7771447007666652</v>
+        <v>3.16046980931259</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6937933644538292</v>
+        <v>3.753191808599868</v>
       </c>
       <c r="P63" t="n">
-        <v>0.5565805676904994</v>
+        <v>3.311617289942672</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.3370343822289237</v>
+        <v>2.19425468182973</v>
       </c>
     </row>
     <row r="64">
@@ -3951,16 +3951,16 @@
         <v>0.2329738747474078</v>
       </c>
       <c r="N64" t="n">
-        <v>0.1636220975616682</v>
+        <v>2.673933311885158</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.6638667441031284</v>
+        <v>2.390506058676875</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.04895785064583358</v>
+        <v>2.120563322874617</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2329738747474078</v>
+        <v>2.393381045978702</v>
       </c>
     </row>
     <row r="65">
@@ -4006,16 +4006,16 @@
         <v>1.442579106075337</v>
       </c>
       <c r="N65" t="n">
-        <v>-0.2087504670316753</v>
+        <v>1.69888019511108</v>
       </c>
       <c r="O65" t="n">
-        <v>0.4490081914433253</v>
+        <v>2.186305991279174</v>
       </c>
       <c r="P65" t="n">
-        <v>1.604556940404539</v>
+        <v>5.711316650608784</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.442579106075337</v>
+        <v>6.101775920476948</v>
       </c>
     </row>
     <row r="66">
@@ -4061,16 +4061,16 @@
         <v>1.405187143178952</v>
       </c>
       <c r="N66" t="n">
-        <v>-0.2084430644916707</v>
+        <v>1.696603060979019</v>
       </c>
       <c r="O66" t="n">
-        <v>0.5583131767872606</v>
+        <v>2.43964074637228</v>
       </c>
       <c r="P66" t="n">
-        <v>1.735803735980771</v>
+        <v>6.065551115227341</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.405187143178952</v>
+        <v>5.42335000757043</v>
       </c>
     </row>
     <row r="67">
@@ -4116,16 +4116,16 @@
         <v>0.7723273148900425</v>
       </c>
       <c r="N67" t="n">
-        <v>-0.01017896439037169</v>
+        <v>2.411044707038378</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7759188354853149</v>
+        <v>3.311909041610814</v>
       </c>
       <c r="P67" t="n">
-        <v>1.457901382827215</v>
+        <v>4.010666150796653</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.7723273148900425</v>
+        <v>2.520648049961857</v>
       </c>
     </row>
     <row r="68">
@@ -4171,16 +4171,16 @@
         <v>1.465318189629918</v>
       </c>
       <c r="N68" t="n">
-        <v>-0.4026736576568073</v>
+        <v>2.173880834870443</v>
       </c>
       <c r="O68" t="n">
-        <v>1.151044850159547</v>
+        <v>4.385777424651145</v>
       </c>
       <c r="P68" t="n">
-        <v>0.5685912499227136</v>
+        <v>2.329143113793798</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.465318189629918</v>
+        <v>5.171785168703477</v>
       </c>
     </row>
     <row r="69">
@@ -4226,16 +4226,16 @@
         <v>0.8218327713556342</v>
       </c>
       <c r="N69" t="n">
-        <v>-0.4164345755893081</v>
+        <v>2.113955549073613</v>
       </c>
       <c r="O69" t="n">
-        <v>0.9255672212063704</v>
+        <v>4.014292691131885</v>
       </c>
       <c r="P69" t="n">
-        <v>0.4447816153937559</v>
+        <v>2.272774336964574</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.8218327713556342</v>
+        <v>3.077541218673352</v>
       </c>
     </row>
     <row r="70">
@@ -4281,16 +4281,16 @@
         <v>1.807998320143672</v>
       </c>
       <c r="N70" t="n">
-        <v>0.3296030415372153</v>
+        <v>2.232781229727742</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8132917944333186</v>
+        <v>2.647594370157924</v>
       </c>
       <c r="P70" t="n">
-        <v>0.327213559170188</v>
+        <v>2.030554793808639</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.807998320143672</v>
+        <v>6.143496928237578</v>
       </c>
     </row>
     <row r="71">
@@ -4336,16 +4336,16 @@
         <v>1.164158744925646</v>
       </c>
       <c r="N71" t="n">
-        <v>0.2640417332181507</v>
+        <v>2.111709874236689</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9196307000796616</v>
+        <v>3.019735140271957</v>
       </c>
       <c r="P71" t="n">
-        <v>0.4616342185788926</v>
+        <v>2.557874042965344</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.164158744925646</v>
+        <v>3.468735720442504</v>
       </c>
     </row>
     <row r="72">
@@ -4391,16 +4391,16 @@
         <v>0.3138101539241401</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6308097856068383</v>
+        <v>3.129489828097908</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.0583830125911776</v>
+        <v>2.451464163397381</v>
       </c>
       <c r="P72" t="n">
-        <v>-0.009137524829689277</v>
+        <v>1.736927292910177</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.3138101539241401</v>
+        <v>2.032492147535225</v>
       </c>
     </row>
     <row r="73">
@@ -4446,16 +4446,16 @@
         <v>1.716667335400052</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.3021652657553237</v>
+        <v>2.015319954984037</v>
       </c>
       <c r="O73" t="n">
-        <v>0.838379419998904</v>
+        <v>2.755263019335296</v>
       </c>
       <c r="P73" t="n">
-        <v>0.2921065416141008</v>
+        <v>2.179941779100302</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.716667335400052</v>
+        <v>5.72782636635829</v>
       </c>
     </row>
     <row r="74">
@@ -4501,16 +4501,16 @@
         <v>-0.3700030041313573</v>
       </c>
       <c r="N74" t="n">
-        <v>0.793723483610684</v>
+        <v>2.353843155251507</v>
       </c>
       <c r="O74" t="n">
-        <v>0.8564297268714522</v>
+        <v>2.827112060215077</v>
       </c>
       <c r="P74" t="n">
-        <v>0.6567840250514339</v>
+        <v>2.563578637754059</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.3700030041313573</v>
+        <v>2.990284289244723</v>
       </c>
     </row>
     <row r="75">
@@ -4556,16 +4556,16 @@
         <v>1.144327172464697</v>
       </c>
       <c r="N75" t="n">
-        <v>-0.06686154200552176</v>
+        <v>1.817923812222056</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.2818761355374819</v>
+        <v>1.871155451842024</v>
       </c>
       <c r="P75" t="n">
-        <v>0.3654196136588496</v>
+        <v>2.081817000038001</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.144327172464697</v>
+        <v>3.205959710478359</v>
       </c>
     </row>
     <row r="76">
@@ -4611,16 +4611,16 @@
         <v>0.4200668025979215</v>
       </c>
       <c r="N76" t="n">
-        <v>-0.1942122988171421</v>
+        <v>1.938124872074562</v>
       </c>
       <c r="O76" t="n">
-        <v>0.2059922776684743</v>
+        <v>2.123881379940996</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.1846493700417701</v>
+        <v>1.62694017659266</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.4200668025979215</v>
+        <v>2.607881011880355</v>
       </c>
     </row>
     <row r="77">
@@ -4666,16 +4666,16 @@
         <v>-0.3905851583123481</v>
       </c>
       <c r="N77" t="n">
-        <v>-0.4257665605455004</v>
+        <v>2.104350674941642</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.4068925846519474</v>
+        <v>2.741093892985468</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.6191263220724619</v>
+        <v>2.659161810097509</v>
       </c>
       <c r="Q77" t="n">
-        <v>-0.3905851583123481</v>
+        <v>2.968923920281497</v>
       </c>
     </row>
     <row r="78">
@@ -4721,16 +4721,16 @@
         <v>-0.3841465442385455</v>
       </c>
       <c r="N78" t="n">
-        <v>-0.4146355058676669</v>
+        <v>2.133628615485537</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.0133145013292202</v>
+        <v>3.068247657398013</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.580035317316124</v>
+        <v>2.640404703875092</v>
       </c>
       <c r="Q78" t="n">
-        <v>-0.3841465442385455</v>
+        <v>2.899270593747942</v>
       </c>
     </row>
     <row r="79">
@@ -4776,16 +4776,16 @@
         <v>0.2636142057773563</v>
       </c>
       <c r="N79" t="n">
-        <v>-0.6282606980785319</v>
+        <v>2.112997151441209</v>
       </c>
       <c r="O79" t="n">
-        <v>0.2153583973843643</v>
+        <v>3.502807521842967</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.003096305869978088</v>
+        <v>2.274278484979295</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.2636142057773563</v>
+        <v>2.093427208954727</v>
       </c>
     </row>
     <row r="80">
@@ -4831,16 +4831,16 @@
         <v>-0.02841630837434097</v>
       </c>
       <c r="N80" t="n">
-        <v>-0.1566089467069254</v>
+        <v>1.932966785769987</v>
       </c>
       <c r="O80" t="n">
-        <v>0.1581371069857402</v>
+        <v>1.748286469128667</v>
       </c>
       <c r="P80" t="n">
-        <v>0.7523536088185613</v>
+        <v>2.753936627156839</v>
       </c>
       <c r="Q80" t="n">
-        <v>-0.02841630837434097</v>
+        <v>2.468471316741385</v>
       </c>
     </row>
     <row r="81">
@@ -4886,16 +4886,16 @@
         <v>0.8518609217855687</v>
       </c>
       <c r="N81" t="n">
-        <v>-0.1317344113758734</v>
+        <v>2.349299874293826</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2461536224375619</v>
+        <v>1.808073114415025</v>
       </c>
       <c r="P81" t="n">
-        <v>0.6477882628695364</v>
+        <v>2.695966909056512</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8518609217855687</v>
+        <v>2.853166725748832</v>
       </c>
     </row>
     <row r="82">
@@ -4941,16 +4941,16 @@
         <v>0.01385184631168096</v>
       </c>
       <c r="N82" t="n">
-        <v>1.334431352395432</v>
+        <v>4.747949915963342</v>
       </c>
       <c r="O82" t="n">
-        <v>1.390166896132554</v>
+        <v>4.799098027123957</v>
       </c>
       <c r="P82" t="n">
-        <v>1.746876365946979</v>
+        <v>6.075781527502491</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.01385184631168096</v>
+        <v>2.110990587059982</v>
       </c>
     </row>
     <row r="83">
@@ -4996,16 +4996,16 @@
         <v>0.6138389424542274</v>
       </c>
       <c r="N83" t="n">
-        <v>-0.529912317986746</v>
+        <v>2.986709802213134</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.07919026806202206</v>
+        <v>1.994547328939827</v>
       </c>
       <c r="P83" t="n">
-        <v>0.03316766911343436</v>
+        <v>2.158226647141207</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.6138389424542274</v>
+        <v>2.158555361438043</v>
       </c>
     </row>
     <row r="84">
@@ -5051,16 +5051,16 @@
         <v>-0.3588727987862987</v>
       </c>
       <c r="N84" t="n">
-        <v>-0.557484946621655</v>
+        <v>2.31849106118982</v>
       </c>
       <c r="O84" t="n">
-        <v>0.4714170902655583</v>
+        <v>3.292799636407052</v>
       </c>
       <c r="P84" t="n">
-        <v>0.6198394895884144</v>
+        <v>3.507684937231446</v>
       </c>
       <c r="Q84" t="n">
-        <v>-0.3588727987862987</v>
+        <v>2.666646477509557</v>
       </c>
     </row>
     <row r="85">
@@ -5106,16 +5106,16 @@
         <v>1.169060917720563</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.6903559318423659</v>
+        <v>3.153177584365527</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.07279291053892557</v>
+        <v>2.093256864675287</v>
       </c>
       <c r="P85" t="n">
-        <v>1.120615767131277</v>
+        <v>3.280422504252338</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.169060917720563</v>
+        <v>3.329964833606135</v>
       </c>
     </row>
     <row r="86">
@@ -5161,16 +5161,16 @@
         <v>0.08371672798459777</v>
       </c>
       <c r="N86" t="n">
-        <v>-0.8698164803358434</v>
+        <v>2.651336864961154</v>
       </c>
       <c r="O86" t="n">
-        <v>0.4280236222307752</v>
+        <v>3.560050131332161</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.01963001972291462</v>
+        <v>2.738426034398638</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.08371672798459777</v>
+        <v>3.20830607393055</v>
       </c>
     </row>
     <row r="87">
@@ -5216,16 +5216,16 @@
         <v>1.817057854933396</v>
       </c>
       <c r="N87" t="n">
-        <v>-0.7073938529102642</v>
+        <v>3.381535689794238</v>
       </c>
       <c r="O87" t="n">
-        <v>0.6997423564269702</v>
+        <v>2.242577090908176</v>
       </c>
       <c r="P87" t="n">
-        <v>0.8457004130588145</v>
+        <v>2.835584883339699</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.817057854933396</v>
+        <v>5.798152772818958</v>
       </c>
     </row>
     <row r="88">
@@ -5271,16 +5271,16 @@
         <v>0.3465501737772265</v>
       </c>
       <c r="N88" t="n">
-        <v>0.4165733176534517</v>
+        <v>2.695261285836646</v>
       </c>
       <c r="O88" t="n">
-        <v>1.103283774881147</v>
+        <v>3.065204062445879</v>
       </c>
       <c r="P88" t="n">
-        <v>0.7398542516604258</v>
+        <v>2.028486447066311</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.3465501737772265</v>
+        <v>1.841234079508311</v>
       </c>
     </row>
     <row r="89">
@@ -5326,16 +5326,16 @@
         <v>-0.2931343765801033</v>
       </c>
       <c r="N89" t="n">
-        <v>1.479087686597536</v>
+        <v>3.890083758884697</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9195328501944956</v>
+        <v>2.966716958513078</v>
       </c>
       <c r="P89" t="n">
-        <v>1.32266100852581</v>
+        <v>3.720673230570456</v>
       </c>
       <c r="Q89" t="n">
-        <v>-0.2931343765801033</v>
+        <v>2.447358243578827</v>
       </c>
     </row>
     <row r="90">
@@ -5381,16 +5381,16 @@
         <v>0.7431955953433684</v>
       </c>
       <c r="N90" t="n">
-        <v>-0.313574758583215</v>
+        <v>1.761867567107139</v>
       </c>
       <c r="O90" t="n">
-        <v>1.483062048961871</v>
+        <v>5.158617252014105</v>
       </c>
       <c r="P90" t="n">
-        <v>1.436142251058264</v>
+        <v>5.311633366050152</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.7431955953433684</v>
+        <v>2.210014694170935</v>
       </c>
     </row>
     <row r="91">
@@ -5436,16 +5436,16 @@
         <v>0.5729586529959684</v>
       </c>
       <c r="N91" t="n">
-        <v>0.1464348355047468</v>
+        <v>1.917828455321447</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.02956713522670356</v>
+        <v>2.021964926403184</v>
       </c>
       <c r="P91" t="n">
-        <v>0.4827159867825117</v>
+        <v>2.338445927951581</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.5729586529959684</v>
+        <v>3.004744478264058</v>
       </c>
     </row>
     <row r="92">
@@ -5491,16 +5491,16 @@
         <v>0.7840236727933673</v>
       </c>
       <c r="N92" t="n">
-        <v>-0.853738301409259</v>
+        <v>3.535854390527719</v>
       </c>
       <c r="O92" t="n">
-        <v>0.6445881752116721</v>
+        <v>2.352769207160743</v>
       </c>
       <c r="P92" t="n">
-        <v>1.326512934943359</v>
+        <v>4.166430736413073</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.7840236727933673</v>
+        <v>3.755815960909802</v>
       </c>
     </row>
     <row r="93">
@@ -5546,16 +5546,16 @@
         <v>0.6223999902317552</v>
       </c>
       <c r="N93" t="n">
-        <v>-0.8540940814701317</v>
+        <v>3.534694541885432</v>
       </c>
       <c r="O93" t="n">
-        <v>0.1482284768987941</v>
+        <v>1.960065352545799</v>
       </c>
       <c r="P93" t="n">
-        <v>0.8723648958617197</v>
+        <v>3.06150638009229</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.6223999902317552</v>
+        <v>2.747973308317109</v>
       </c>
     </row>
     <row r="94">
@@ -5601,16 +5601,16 @@
         <v>0.7694234712527986</v>
       </c>
       <c r="N94" t="n">
-        <v>-0.8511372831319584</v>
+        <v>3.523781452480952</v>
       </c>
       <c r="O94" t="n">
-        <v>0.3619179189271293</v>
+        <v>1.976914978473218</v>
       </c>
       <c r="P94" t="n">
-        <v>1.102885671511329</v>
+        <v>3.609065483539692</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.7694234712527986</v>
+        <v>3.444125135242795</v>
       </c>
     </row>
     <row r="95">
@@ -5656,16 +5656,16 @@
         <v>0.7718834414443445</v>
       </c>
       <c r="N95" t="n">
-        <v>-0.8511372831319584</v>
+        <v>3.523781452480952</v>
       </c>
       <c r="O95" t="n">
-        <v>0.2302817027550401</v>
+        <v>1.745813484578268</v>
       </c>
       <c r="P95" t="n">
-        <v>0.9654336077362219</v>
+        <v>3.236502434881175</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.7718834414443445</v>
+        <v>3.431654783721183</v>
       </c>
     </row>
     <row r="96">
@@ -5711,16 +5711,16 @@
         <v>-0.5189349043466555</v>
       </c>
       <c r="N96" t="n">
-        <v>-0.3259406120997248</v>
+        <v>3.725002428135052</v>
       </c>
       <c r="O96" t="n">
-        <v>0.6288325786248344</v>
+        <v>2.238423264362911</v>
       </c>
       <c r="P96" t="n">
-        <v>0.4363352100496878</v>
+        <v>1.946012440113708</v>
       </c>
       <c r="Q96" t="n">
-        <v>-0.5189349043466555</v>
+        <v>3.011284239077933</v>
       </c>
     </row>
     <row r="97">
@@ -5766,16 +5766,16 @@
         <v>2.018325010146476</v>
       </c>
       <c r="N97" t="n">
-        <v>1.113928967308104</v>
+        <v>4.682847286179733</v>
       </c>
       <c r="O97" t="n">
-        <v>0.5155299362771917</v>
+        <v>2.26267025775375</v>
       </c>
       <c r="P97" t="n">
-        <v>0.06112145662563517</v>
+        <v>1.813506326405663</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.018325010146476</v>
+        <v>7.036553462464563</v>
       </c>
     </row>
     <row r="98">
@@ -5821,16 +5821,16 @@
         <v>1.374724102665027</v>
       </c>
       <c r="N98" t="n">
-        <v>-0.7328305770575496</v>
+        <v>2.839327436497264</v>
       </c>
       <c r="O98" t="n">
-        <v>-0.102463772240782</v>
+        <v>2.938520699917127</v>
       </c>
       <c r="P98" t="n">
-        <v>0.2933872784323047</v>
+        <v>2.824940380638511</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.374724102665027</v>
+        <v>4.368455360528966</v>
       </c>
     </row>
     <row r="99">
@@ -5876,16 +5876,16 @@
         <v>0.4313491953641709</v>
       </c>
       <c r="N99" t="n">
-        <v>-1.178589343787342</v>
+        <v>4.386134591150871</v>
       </c>
       <c r="O99" t="n">
-        <v>0.2142063178875989</v>
+        <v>1.981753702044634</v>
       </c>
       <c r="P99" t="n">
-        <v>0.3264446372276302</v>
+        <v>1.63106115810193</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.4313491953641709</v>
+        <v>2.70811150401909</v>
       </c>
     </row>
     <row r="100">
@@ -5931,16 +5931,16 @@
         <v>2.039261564476279</v>
       </c>
       <c r="N100" t="n">
-        <v>0.5709867792397429</v>
+        <v>3.350162487501901</v>
       </c>
       <c r="O100" t="n">
-        <v>0.5154307904900313</v>
+        <v>2.193912710737533</v>
       </c>
       <c r="P100" t="n">
-        <v>0.1030764513775317</v>
+        <v>2.270213403106334</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.039261564476279</v>
+        <v>7.184957309787841</v>
       </c>
     </row>
     <row r="101">
@@ -5986,16 +5986,16 @@
         <v>0.09366278652273832</v>
       </c>
       <c r="N101" t="n">
-        <v>-0.03487033320358404</v>
+        <v>1.722377207123622</v>
       </c>
       <c r="O101" t="n">
-        <v>1.198136718681414</v>
+        <v>3.24143600220191</v>
       </c>
       <c r="P101" t="n">
-        <v>1.082129723680332</v>
+        <v>3.293548579272852</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.09366278652273832</v>
+        <v>2.171280201164884</v>
       </c>
     </row>
     <row r="102">
@@ -6041,16 +6041,16 @@
         <v>0.01346256389089326</v>
       </c>
       <c r="N102" t="n">
-        <v>-1.321303658311387</v>
+        <v>4.620995243378394</v>
       </c>
       <c r="O102" t="n">
-        <v>-0.1878639176903843</v>
+        <v>2.251669298513149</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.1297532319707818</v>
+        <v>2.454527806884834</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.01346256389089326</v>
+        <v>2.588496580898251</v>
       </c>
     </row>
     <row r="103">
@@ -6096,16 +6096,16 @@
         <v>0.1625477110335607</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.5169605136719655</v>
+        <v>2.446653102561807</v>
       </c>
       <c r="O103" t="n">
-        <v>0.6056204097792184</v>
+        <v>2.280661978409841</v>
       </c>
       <c r="P103" t="n">
-        <v>0.5703266078375611</v>
+        <v>2.129447421114465</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.1625477110335607</v>
+        <v>3.11861879873264</v>
       </c>
     </row>
     <row r="104">
@@ -6151,16 +6151,16 @@
         <v>-0.2055001771791231</v>
       </c>
       <c r="N104" t="n">
-        <v>-0.4890200777234498</v>
+        <v>2.921901687119953</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.4182389393269928</v>
+        <v>2.406495431757139</v>
       </c>
       <c r="P104" t="n">
-        <v>0.1073724411499049</v>
+        <v>2.749313827544034</v>
       </c>
       <c r="Q104" t="n">
-        <v>-0.2055001771791231</v>
+        <v>1.905711556547769</v>
       </c>
     </row>
     <row r="105">
@@ -6206,16 +6206,16 @@
         <v>0.2485897962663547</v>
       </c>
       <c r="N105" t="n">
-        <v>1.473543727272435</v>
+        <v>5.99321316170626</v>
       </c>
       <c r="O105" t="n">
-        <v>1.034206742190171</v>
+        <v>3.970490472420387</v>
       </c>
       <c r="P105" t="n">
-        <v>0.9654769605992003</v>
+        <v>3.697240524557061</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.2485897962663547</v>
+        <v>2.19236374232896</v>
       </c>
     </row>
     <row r="106">
@@ -6261,16 +6261,16 @@
         <v>1.959219698629435</v>
       </c>
       <c r="N106" t="n">
-        <v>-0.02818551336127826</v>
+        <v>1.643852905524658</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.1743271361601643</v>
+        <v>1.405570467493981</v>
       </c>
       <c r="P106" t="n">
-        <v>1.458647602550522</v>
+        <v>4.733260753705449</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.959219698629435</v>
+        <v>6.625017197291986</v>
       </c>
     </row>
     <row r="107">
@@ -6316,16 +6316,16 @@
         <v>-0.2718314633219025</v>
       </c>
       <c r="N107" t="n">
-        <v>-0.1468529536329486</v>
+        <v>2.06666342321161</v>
       </c>
       <c r="O107" t="n">
-        <v>0.513308142737759</v>
+        <v>1.804945406595595</v>
       </c>
       <c r="P107" t="n">
-        <v>0.6329961642506735</v>
+        <v>2.320317730318637</v>
       </c>
       <c r="Q107" t="n">
-        <v>-0.2718314633219025</v>
+        <v>1.452341681033897</v>
       </c>
     </row>
     <row r="108">
@@ -6371,16 +6371,16 @@
         <v>-0.2311901870037114</v>
       </c>
       <c r="N108" t="n">
-        <v>-0.1455984898531595</v>
+        <v>2.069944622775412</v>
       </c>
       <c r="O108" t="n">
-        <v>0.4862420313484679</v>
+        <v>1.771843189515343</v>
       </c>
       <c r="P108" t="n">
-        <v>0.6313695225479449</v>
+        <v>2.252239568238902</v>
       </c>
       <c r="Q108" t="n">
-        <v>-0.2311901870037114</v>
+        <v>1.412095941841935</v>
       </c>
     </row>
     <row r="109">
@@ -6426,16 +6426,16 @@
         <v>-0.1775981358207351</v>
       </c>
       <c r="N109" t="n">
-        <v>-0.1531445605412642</v>
+        <v>2.06330381051703</v>
       </c>
       <c r="O109" t="n">
-        <v>0.5251437448010409</v>
+        <v>1.830958456906907</v>
       </c>
       <c r="P109" t="n">
-        <v>0.6477457114631131</v>
+        <v>2.2871807134476</v>
       </c>
       <c r="Q109" t="n">
-        <v>-0.1775981358207351</v>
+        <v>1.397165520746257</v>
       </c>
     </row>
     <row r="110">
@@ -6481,16 +6481,16 @@
         <v>0.1385297351647255</v>
       </c>
       <c r="N110" t="n">
-        <v>-0.1297859489784181</v>
+        <v>1.846683611676881</v>
       </c>
       <c r="O110" t="n">
-        <v>1.158149239202242</v>
+        <v>3.249568411899355</v>
       </c>
       <c r="P110" t="n">
-        <v>1.095810392987846</v>
+        <v>3.455433472542558</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.1385297351647255</v>
+        <v>1.937946187876738</v>
       </c>
     </row>
     <row r="111">
@@ -6536,16 +6536,16 @@
         <v>0.1669761372678946</v>
       </c>
       <c r="N111" t="n">
-        <v>-0.6427460456146149</v>
+        <v>3.244564425764419</v>
       </c>
       <c r="O111" t="n">
-        <v>-0.003891035377456847</v>
+        <v>1.592489122548611</v>
       </c>
       <c r="P111" t="n">
-        <v>0.5529041693360355</v>
+        <v>2.102430530686963</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.1669761372678946</v>
+        <v>1.825232839160351</v>
       </c>
     </row>
     <row r="112">
@@ -6591,16 +6591,16 @@
         <v>-0.5819835147348986</v>
       </c>
       <c r="N112" t="n">
-        <v>-1.461474507553879</v>
+        <v>4.585151597266321</v>
       </c>
       <c r="O112" t="n">
-        <v>0.7201608750809461</v>
+        <v>3.374754396545693</v>
       </c>
       <c r="P112" t="n">
-        <v>0.2673016157923708</v>
+        <v>2.671200616482553</v>
       </c>
       <c r="Q112" t="n">
-        <v>-0.5819835147348986</v>
+        <v>2.033986069718851</v>
       </c>
     </row>
     <row r="113">
@@ -6646,16 +6646,16 @@
         <v>-0.5424117289566401</v>
       </c>
       <c r="N113" t="n">
-        <v>-1.464832466199299</v>
+        <v>4.593491868580291</v>
       </c>
       <c r="O113" t="n">
-        <v>0.7296450098281986</v>
+        <v>3.31114724225259</v>
       </c>
       <c r="P113" t="n">
-        <v>0.2836887249030162</v>
+        <v>2.63125866452542</v>
       </c>
       <c r="Q113" t="n">
-        <v>-0.5424117289566401</v>
+        <v>2.003106159322683</v>
       </c>
     </row>
     <row r="114">
@@ -6701,16 +6701,16 @@
         <v>-0.3434726748476709</v>
       </c>
       <c r="N114" t="n">
-        <v>0.356166577963948</v>
+        <v>4.485658977923224</v>
       </c>
       <c r="O114" t="n">
-        <v>0.9068118364364541</v>
+        <v>2.910105027130542</v>
       </c>
       <c r="P114" t="n">
-        <v>0.9457262944238852</v>
+        <v>2.98615244122486</v>
       </c>
       <c r="Q114" t="n">
-        <v>-0.3434726748476709</v>
+        <v>1.666645238763764</v>
       </c>
     </row>
     <row r="115">
@@ -6756,16 +6756,16 @@
         <v>1.209701038237202</v>
       </c>
       <c r="N115" t="n">
-        <v>-0.3330821667627038</v>
+        <v>2.434979028731752</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.1196914644264212</v>
+        <v>2.677465739893445</v>
       </c>
       <c r="P115" t="n">
-        <v>0.4498917846483072</v>
+        <v>2.338053033847983</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.209701038237202</v>
+        <v>3.966786179530504</v>
       </c>
     </row>
     <row r="116">
@@ -6811,16 +6811,16 @@
         <v>0.6455718442599812</v>
       </c>
       <c r="N116" t="n">
-        <v>-0.6242764253692794</v>
+        <v>3.236406756999419</v>
       </c>
       <c r="O116" t="n">
-        <v>0.3686793556701993</v>
+        <v>1.667696824538361</v>
       </c>
       <c r="P116" t="n">
-        <v>0.83731011867928</v>
+        <v>2.6529537308121</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.6455718442599812</v>
+        <v>2.97205783695418</v>
       </c>
     </row>
     <row r="117">
@@ -6866,16 +6866,16 @@
         <v>0.6560070224748924</v>
       </c>
       <c r="N117" t="n">
-        <v>-0.6242764253692794</v>
+        <v>3.236406756999419</v>
       </c>
       <c r="O117" t="n">
-        <v>0.3842393231100205</v>
+        <v>1.838751314120671</v>
       </c>
       <c r="P117" t="n">
-        <v>0.8818285624756417</v>
+        <v>2.80054544031543</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.6560070224748924</v>
+        <v>2.93002168351181</v>
       </c>
     </row>
     <row r="118">
@@ -6921,16 +6921,16 @@
         <v>0.5574053732576713</v>
       </c>
       <c r="N118" t="n">
-        <v>-0.6221109310540621</v>
+        <v>3.224759393797612</v>
       </c>
       <c r="O118" t="n">
-        <v>0.04821198461052668</v>
+        <v>1.636738515268728</v>
       </c>
       <c r="P118" t="n">
-        <v>0.5808787357743331</v>
+        <v>2.225626418508077</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.5574053732576713</v>
+        <v>2.524045530074496</v>
       </c>
     </row>
     <row r="119">
@@ -6976,16 +6976,16 @@
         <v>1.987374270437982</v>
       </c>
       <c r="N119" t="n">
-        <v>1.144586062126018</v>
+        <v>4.757333165172951</v>
       </c>
       <c r="O119" t="n">
-        <v>0.2476417709205918</v>
+        <v>1.752181523213838</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.2637160781871608</v>
+        <v>1.427038489608474</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.987374270437982</v>
+        <v>6.758300822621436</v>
       </c>
     </row>
     <row r="120">
@@ -7031,16 +7031,16 @@
         <v>2.053515453421802</v>
       </c>
       <c r="N120" t="n">
-        <v>1.07438871969738</v>
+        <v>4.565820295131803</v>
       </c>
       <c r="O120" t="n">
-        <v>0.2732562111935302</v>
+        <v>1.860558699099842</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.284464897535382</v>
+        <v>1.472245120364638</v>
       </c>
       <c r="Q120" t="n">
-        <v>2.053515453421802</v>
+        <v>7.179351217442822</v>
       </c>
     </row>
     <row r="121">
@@ -7086,16 +7086,16 @@
         <v>1.956906581976557</v>
       </c>
       <c r="N121" t="n">
-        <v>1.075038818619613</v>
+        <v>4.5661642996388</v>
       </c>
       <c r="O121" t="n">
-        <v>0.2300348211886464</v>
+        <v>1.906425888001441</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.3317448749532065</v>
+        <v>1.474708259112799</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.956906581976557</v>
+        <v>6.694122463633581</v>
       </c>
     </row>
     <row r="122">
@@ -7141,16 +7141,16 @@
         <v>1.93701534202975</v>
       </c>
       <c r="N122" t="n">
-        <v>1.07257072819703</v>
+        <v>4.563333978605023</v>
       </c>
       <c r="O122" t="n">
-        <v>0.2759032026529352</v>
+        <v>2.022357168511046</v>
       </c>
       <c r="P122" t="n">
-        <v>-0.3257490710296829</v>
+        <v>1.456784529231233</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.93701534202975</v>
+        <v>6.602295347649649</v>
       </c>
     </row>
     <row r="123">
@@ -7196,16 +7196,16 @@
         <v>0.3617742166433596</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.1422335388084321</v>
+        <v>2.158075144312893</v>
       </c>
       <c r="O123" t="n">
-        <v>1.0423044133773</v>
+        <v>2.770015070471922</v>
       </c>
       <c r="P123" t="n">
-        <v>0.9488769854601882</v>
+        <v>2.566521837130856</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.3617742166433596</v>
+        <v>2.759140081390335</v>
       </c>
     </row>
     <row r="124">
@@ -7251,16 +7251,16 @@
         <v>-0.4640428123881237</v>
       </c>
       <c r="N124" t="n">
-        <v>0.01029833864277614</v>
+        <v>1.678079439773932</v>
       </c>
       <c r="O124" t="n">
-        <v>1.054458778273198</v>
+        <v>3.438973533198995</v>
       </c>
       <c r="P124" t="n">
-        <v>0.9735711472860638</v>
+        <v>3.733181237051733</v>
       </c>
       <c r="Q124" t="n">
-        <v>-0.4640428123881237</v>
+        <v>2.364234140778249</v>
       </c>
     </row>
     <row r="125">
@@ -7306,16 +7306,16 @@
         <v>1.08987997484573</v>
       </c>
       <c r="N125" t="n">
-        <v>-1.834133053997594</v>
+        <v>5.985500514242062</v>
       </c>
       <c r="O125" t="n">
-        <v>1.578988663553119</v>
+        <v>5.204736613841667</v>
       </c>
       <c r="P125" t="n">
-        <v>1.887553994923033</v>
+        <v>6.632767319418935</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.08987997484573</v>
+        <v>4.16844272578054</v>
       </c>
     </row>
     <row r="126">
@@ -7361,16 +7361,16 @@
         <v>1.11036999461635</v>
       </c>
       <c r="N126" t="n">
-        <v>0.7278114277862883</v>
+        <v>2.541516554362009</v>
       </c>
       <c r="O126" t="n">
-        <v>0.594690696245651</v>
+        <v>2.048190148011711</v>
       </c>
       <c r="P126" t="n">
-        <v>0.6663197303815568</v>
+        <v>2.06220409922821</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.11036999461635</v>
+        <v>4.11967475555911</v>
       </c>
     </row>
     <row r="127">
@@ -7416,16 +7416,16 @@
         <v>0.01890743093994815</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.8044380749887159</v>
+        <v>3.905131957689279</v>
       </c>
       <c r="O127" t="n">
-        <v>0.4436377409830431</v>
+        <v>2.300296231658416</v>
       </c>
       <c r="P127" t="n">
-        <v>0.06754713586210305</v>
+        <v>1.816995185296082</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.01890743093994815</v>
+        <v>2.804874062512699</v>
       </c>
     </row>
     <row r="128">
@@ -7471,16 +7471,16 @@
         <v>0.02943011797408804</v>
       </c>
       <c r="N128" t="n">
-        <v>-0.8054540200335988</v>
+        <v>3.924809117280727</v>
       </c>
       <c r="O128" t="n">
-        <v>0.4283491603980819</v>
+        <v>2.20178151566139</v>
       </c>
       <c r="P128" t="n">
-        <v>0.1182484616289046</v>
+        <v>1.723579173216993</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.02943011797408804</v>
+        <v>2.694202767023921</v>
       </c>
     </row>
     <row r="129">
@@ -7526,16 +7526,16 @@
         <v>0.5711354491905105</v>
       </c>
       <c r="N129" t="n">
-        <v>-0.8764096102516983</v>
+        <v>2.998687125198524</v>
       </c>
       <c r="O129" t="n">
-        <v>0.07365486994635519</v>
+        <v>1.859191050868176</v>
       </c>
       <c r="P129" t="n">
-        <v>0.2400759634456426</v>
+        <v>2.232594822853957</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.5711354491905105</v>
+        <v>2.175819257529092</v>
       </c>
     </row>
     <row r="130">
@@ -7581,16 +7581,16 @@
         <v>0.1546102171315706</v>
       </c>
       <c r="N130" t="n">
-        <v>-0.3358686589833831</v>
+        <v>1.762389195967261</v>
       </c>
       <c r="O130" t="n">
-        <v>0.04923953772335908</v>
+        <v>1.916545831631408</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.1189182417830539</v>
+        <v>2.441531250260057</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.1546102171315706</v>
+        <v>2.06626933830494</v>
       </c>
     </row>
     <row r="131">
@@ -7636,16 +7636,16 @@
         <v>-0.3561601192633565</v>
       </c>
       <c r="N131" t="n">
-        <v>-0.2668855766589613</v>
+        <v>1.924765334445153</v>
       </c>
       <c r="O131" t="n">
-        <v>1.054300588849178</v>
+        <v>3.426711819344587</v>
       </c>
       <c r="P131" t="n">
-        <v>0.9734984964607476</v>
+        <v>3.626046577776493</v>
       </c>
       <c r="Q131" t="n">
-        <v>-0.3561601192633565</v>
+        <v>2.37938521987573</v>
       </c>
     </row>
     <row r="132">
@@ -7691,16 +7691,16 @@
         <v>-0.7416416100709141</v>
       </c>
       <c r="N132" t="n">
-        <v>0.6143008455517777</v>
+        <v>3.871931536251072</v>
       </c>
       <c r="O132" t="n">
-        <v>0.8123878641879972</v>
+        <v>2.748219373606106</v>
       </c>
       <c r="P132" t="n">
-        <v>0.9038587922955256</v>
+        <v>2.877179881082684</v>
       </c>
       <c r="Q132" t="n">
-        <v>-0.7416416100709141</v>
+        <v>2.258114742262809</v>
       </c>
     </row>
     <row r="133">
@@ -7746,16 +7746,16 @@
         <v>0.396893292386301</v>
       </c>
       <c r="N133" t="n">
-        <v>-0.4257364874156922</v>
+        <v>1.806862069658791</v>
       </c>
       <c r="O133" t="n">
-        <v>-0.2806333043907524</v>
+        <v>2.292030313840136</v>
       </c>
       <c r="P133" t="n">
-        <v>0.4002067866681687</v>
+        <v>2.052048931309</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.396893292386301</v>
+        <v>2.479167275471545</v>
       </c>
     </row>
     <row r="134">
@@ -7801,16 +7801,16 @@
         <v>0.6935669532822312</v>
       </c>
       <c r="N134" t="n">
-        <v>-0.1447806264906804</v>
+        <v>1.916127955316866</v>
       </c>
       <c r="O134" t="n">
-        <v>0.5917662777943888</v>
+        <v>2.50568079821855</v>
       </c>
       <c r="P134" t="n">
-        <v>0.9665670621762622</v>
+        <v>3.180720684407159</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.6935669532822312</v>
+        <v>2.135597295719478</v>
       </c>
     </row>
     <row r="135">
@@ -7856,16 +7856,16 @@
         <v>0.7282652659418688</v>
       </c>
       <c r="N135" t="n">
-        <v>-0.1188463121418959</v>
+        <v>1.880041751574475</v>
       </c>
       <c r="O135" t="n">
-        <v>0.6327986051163161</v>
+        <v>2.545706954832667</v>
       </c>
       <c r="P135" t="n">
-        <v>0.9959366281351764</v>
+        <v>3.23732717185707</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.7282652659418688</v>
+        <v>2.291434863016776</v>
       </c>
     </row>
     <row r="136">
@@ -7911,16 +7911,16 @@
         <v>0.2303844537774369</v>
       </c>
       <c r="N136" t="n">
-        <v>-0.2691119048908883</v>
+        <v>2.490021231943272</v>
       </c>
       <c r="O136" t="n">
-        <v>-0.2751506985247285</v>
+        <v>2.201829991691547</v>
       </c>
       <c r="P136" t="n">
-        <v>0.2383690379791087</v>
+        <v>1.818094180477328</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.2303844537774369</v>
+        <v>1.891111775467928</v>
       </c>
     </row>
     <row r="137">
@@ -7966,16 +7966,16 @@
         <v>0.5927091383381253</v>
       </c>
       <c r="N137" t="n">
-        <v>-0.278938510517165</v>
+        <v>3.479456484399236</v>
       </c>
       <c r="O137" t="n">
-        <v>0.1497415792189218</v>
+        <v>2.10303506795961</v>
       </c>
       <c r="P137" t="n">
-        <v>0.8481572576204242</v>
+        <v>3.266687719895539</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.5927091383381253</v>
+        <v>3.013064395433069</v>
       </c>
     </row>
     <row r="138">
@@ -8021,16 +8021,16 @@
         <v>0.04099880373687847</v>
       </c>
       <c r="N138" t="n">
-        <v>-0.0832961220594949</v>
+        <v>1.898978008455316</v>
       </c>
       <c r="O138" t="n">
-        <v>-0.2914613565042717</v>
+        <v>2.15925463270922</v>
       </c>
       <c r="P138" t="n">
-        <v>0.0897145951991066</v>
+        <v>2.016632449557255</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.04099880373687847</v>
+        <v>1.713983128310712</v>
       </c>
     </row>
     <row r="139">
@@ -8076,16 +8076,16 @@
         <v>1.496809510561799</v>
       </c>
       <c r="N139" t="n">
-        <v>-0.4148556097836817</v>
+        <v>2.624749006480612</v>
       </c>
       <c r="O139" t="n">
-        <v>1.173620262811895</v>
+        <v>3.107215023568127</v>
       </c>
       <c r="P139" t="n">
-        <v>1.888212695005548</v>
+        <v>6.109462656117425</v>
       </c>
       <c r="Q139" t="n">
-        <v>1.496809510561799</v>
+        <v>4.148768299482748</v>
       </c>
     </row>
     <row r="140">
@@ -8131,16 +8131,16 @@
         <v>1.203589658555413</v>
       </c>
       <c r="N140" t="n">
-        <v>-0.5009771415774239</v>
+        <v>3.219013779633953</v>
       </c>
       <c r="O140" t="n">
-        <v>1.104268647477316</v>
+        <v>2.899349258303423</v>
       </c>
       <c r="P140" t="n">
-        <v>1.798660032591514</v>
+        <v>5.716239694792145</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.203589658555413</v>
+        <v>3.146464985219305</v>
       </c>
     </row>
     <row r="141">
@@ -8186,16 +8186,16 @@
         <v>0.6669589023939559</v>
       </c>
       <c r="N141" t="n">
-        <v>-0.5939871210270007</v>
+        <v>2.173906169343337</v>
       </c>
       <c r="O141" t="n">
-        <v>0.5142697442836075</v>
+        <v>3.511966138723194</v>
       </c>
       <c r="P141" t="n">
-        <v>-0.1635852227869894</v>
+        <v>2.766217430875643</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.6669589023939559</v>
+        <v>2.363120445113386</v>
       </c>
     </row>
     <row r="142">
@@ -8241,16 +8241,16 @@
         <v>1.865097837072834</v>
       </c>
       <c r="N142" t="n">
-        <v>-0.6524021022046768</v>
+        <v>2.836817961940493</v>
       </c>
       <c r="O142" t="n">
-        <v>0.7367709763415022</v>
+        <v>3.476461129615544</v>
       </c>
       <c r="P142" t="n">
-        <v>0.9933708609753811</v>
+        <v>3.127219995829258</v>
       </c>
       <c r="Q142" t="n">
-        <v>1.865097837072834</v>
+        <v>6.234888456403065</v>
       </c>
     </row>
     <row r="143">
@@ -8296,16 +8296,16 @@
         <v>-0.08634555463309482</v>
       </c>
       <c r="N143" t="n">
-        <v>0.02292588915694866</v>
+        <v>2.694079624650403</v>
       </c>
       <c r="O143" t="n">
-        <v>0.4602687630610926</v>
+        <v>2.608697549200188</v>
       </c>
       <c r="P143" t="n">
-        <v>0.09813291764559073</v>
+        <v>1.883487584533877</v>
       </c>
       <c r="Q143" t="n">
-        <v>-0.08634555463309482</v>
+        <v>1.692742467396812</v>
       </c>
     </row>
     <row r="144">
@@ -8351,16 +8351,16 @@
         <v>-0.09843624137056801</v>
       </c>
       <c r="N144" t="n">
-        <v>0.02292588915694866</v>
+        <v>2.694079624650403</v>
       </c>
       <c r="O144" t="n">
-        <v>0.5495933914078337</v>
+        <v>2.665153804422211</v>
       </c>
       <c r="P144" t="n">
-        <v>0.09479696368239135</v>
+        <v>1.892727702339647</v>
       </c>
       <c r="Q144" t="n">
-        <v>-0.09843624137056801</v>
+        <v>1.644037462507216</v>
       </c>
     </row>
     <row r="145">
@@ -8406,16 +8406,16 @@
         <v>-0.09319597592967735</v>
       </c>
       <c r="N145" t="n">
-        <v>0.02292588915694866</v>
+        <v>2.694079624650403</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6868529224365554</v>
+        <v>3.047979428866004</v>
       </c>
       <c r="P145" t="n">
-        <v>0.1549566688122457</v>
+        <v>1.904943240564891</v>
       </c>
       <c r="Q145" t="n">
-        <v>-0.09319597592967735</v>
+        <v>1.774748074301397</v>
       </c>
     </row>
     <row r="146">
@@ -8461,16 +8461,16 @@
         <v>-0.1592586974386867</v>
       </c>
       <c r="N146" t="n">
-        <v>0.05840192510685224</v>
+        <v>2.711466936235652</v>
       </c>
       <c r="O146" t="n">
-        <v>0.5650234127716003</v>
+        <v>2.793878931622345</v>
       </c>
       <c r="P146" t="n">
-        <v>0.1099449949155061</v>
+        <v>1.826554905173593</v>
       </c>
       <c r="Q146" t="n">
-        <v>-0.1592586974386867</v>
+        <v>1.591004388254474</v>
       </c>
     </row>
     <row r="147">
@@ -8516,16 +8516,16 @@
         <v>0.9225185477140642</v>
       </c>
       <c r="N147" t="n">
-        <v>-0.6259486571796081</v>
+        <v>2.28797013104005</v>
       </c>
       <c r="O147" t="n">
-        <v>0.3683864553169384</v>
+        <v>3.348786121811165</v>
       </c>
       <c r="P147" t="n">
-        <v>-0.03829934063532365</v>
+        <v>2.545935464981937</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.9225185477140642</v>
+        <v>3.130025586525469</v>
       </c>
     </row>
     <row r="148">
@@ -8571,16 +8571,16 @@
         <v>0.8610660124069374</v>
       </c>
       <c r="N148" t="n">
-        <v>0.1474008964127563</v>
+        <v>1.946964181461343</v>
       </c>
       <c r="O148" t="n">
-        <v>1.053726415580504</v>
+        <v>3.494309329889867</v>
       </c>
       <c r="P148" t="n">
-        <v>1.164676550816209</v>
+        <v>3.376448219783587</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.8610660124069374</v>
+        <v>2.786610405973256</v>
       </c>
     </row>
     <row r="149">
@@ -8626,16 +8626,16 @@
         <v>-0.383846750258168</v>
       </c>
       <c r="N149" t="n">
-        <v>1.513568379342453</v>
+        <v>3.785529933511415</v>
       </c>
       <c r="O149" t="n">
-        <v>1.252121012456021</v>
+        <v>3.181279569027656</v>
       </c>
       <c r="P149" t="n">
-        <v>0.709017830322681</v>
+        <v>2.222104082345751</v>
       </c>
       <c r="Q149" t="n">
-        <v>-0.383846750258168</v>
+        <v>1.876174857801198</v>
       </c>
     </row>
     <row r="150">
@@ -8681,16 +8681,16 @@
         <v>1.066466462652324</v>
       </c>
       <c r="N150" t="n">
-        <v>-0.5088908806617988</v>
+        <v>2.219755196189399</v>
       </c>
       <c r="O150" t="n">
-        <v>0.9500976352486177</v>
+        <v>4.150612414318013</v>
       </c>
       <c r="P150" t="n">
-        <v>0.3529450881600388</v>
+        <v>3.282201910555818</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.066466462652324</v>
+        <v>3.605808218743581</v>
       </c>
     </row>
     <row r="151">
@@ -8736,16 +8736,16 @@
         <v>1.232640504214449</v>
       </c>
       <c r="N151" t="n">
-        <v>-1.706209675867944</v>
+        <v>5.415827315306346</v>
       </c>
       <c r="O151" t="n">
-        <v>0.8073189074852423</v>
+        <v>3.105873326023943</v>
       </c>
       <c r="P151" t="n">
-        <v>1.200074172462277</v>
+        <v>4.760364748769747</v>
       </c>
       <c r="Q151" t="n">
-        <v>1.232640504214449</v>
+        <v>3.480883232395665</v>
       </c>
     </row>
     <row r="152">
@@ -8791,16 +8791,16 @@
         <v>0.1688341661532023</v>
       </c>
       <c r="N152" t="n">
-        <v>-0.2644424823913619</v>
+        <v>2.300245291187964</v>
       </c>
       <c r="O152" t="n">
-        <v>0.2737029118268113</v>
+        <v>1.969946152137382</v>
       </c>
       <c r="P152" t="n">
-        <v>0.452122164061611</v>
+        <v>2.057252288521217</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.1688341661532023</v>
+        <v>2.211695659748694</v>
       </c>
     </row>
     <row r="153">
@@ -8846,16 +8846,16 @@
         <v>0.5770329225917549</v>
       </c>
       <c r="N153" t="n">
-        <v>-0.3079073891930423</v>
+        <v>2.508940507635844</v>
       </c>
       <c r="O153" t="n">
-        <v>1.87190147892567</v>
+        <v>6.254621222330844</v>
       </c>
       <c r="P153" t="n">
-        <v>2.15764454765909</v>
+        <v>7.558563863851495</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.5770329225917549</v>
+        <v>2.557150411687731</v>
       </c>
     </row>
     <row r="154">
@@ -8901,16 +8901,16 @@
         <v>0.6055071323546487</v>
       </c>
       <c r="N154" t="n">
-        <v>-0.9766779182234542</v>
+        <v>2.493805028333031</v>
       </c>
       <c r="O154" t="n">
-        <v>0.2135977292510058</v>
+        <v>2.483055961442922</v>
       </c>
       <c r="P154" t="n">
-        <v>0.5000381203844945</v>
+        <v>2.542194067407163</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.6055071323546487</v>
+        <v>2.417506931637196</v>
       </c>
     </row>
     <row r="155">
@@ -8956,16 +8956,16 @@
         <v>1.211349708530722</v>
       </c>
       <c r="N155" t="n">
-        <v>-1.186759982067866</v>
+        <v>4.1994978882326</v>
       </c>
       <c r="O155" t="n">
-        <v>-0.137030579391487</v>
+        <v>1.715699632245752</v>
       </c>
       <c r="P155" t="n">
-        <v>0.01477832044665646</v>
+        <v>1.662906548009918</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.211349708530722</v>
+        <v>4.071279920217274</v>
       </c>
     </row>
     <row r="156">
@@ -9011,16 +9011,16 @@
         <v>1.147967864501705</v>
       </c>
       <c r="N156" t="n">
-        <v>-1.195035130941581</v>
+        <v>4.250511832120949</v>
       </c>
       <c r="O156" t="n">
-        <v>-0.1824550130824316</v>
+        <v>1.740125811643805</v>
       </c>
       <c r="P156" t="n">
-        <v>0.02709610029264473</v>
+        <v>1.701090062664541</v>
       </c>
       <c r="Q156" t="n">
-        <v>1.147967864501705</v>
+        <v>3.876361066927996</v>
       </c>
     </row>
     <row r="157">
@@ -9066,16 +9066,16 @@
         <v>2.426513678017744</v>
       </c>
       <c r="N157" t="n">
-        <v>-0.1713768287030163</v>
+        <v>2.562334352930405</v>
       </c>
       <c r="O157" t="n">
-        <v>-0.01258925848759999</v>
+        <v>1.943965123989471</v>
       </c>
       <c r="P157" t="n">
-        <v>1.672515584703557</v>
+        <v>5.73470865631712</v>
       </c>
       <c r="Q157" t="n">
-        <v>2.426513678017744</v>
+        <v>8.406710585979633</v>
       </c>
     </row>
     <row r="158">
@@ -9121,16 +9121,16 @@
         <v>2.394190351157321</v>
       </c>
       <c r="N158" t="n">
-        <v>-0.1358950767010747</v>
+        <v>2.495136461103616</v>
       </c>
       <c r="O158" t="n">
-        <v>-0.09240778769596648</v>
+        <v>2.156068052930057</v>
       </c>
       <c r="P158" t="n">
-        <v>2.007543053550242</v>
+        <v>7.0208085041597</v>
       </c>
       <c r="Q158" t="n">
-        <v>2.394190351157321</v>
+        <v>8.275646063734445</v>
       </c>
     </row>
     <row r="159">
@@ -9176,16 +9176,16 @@
         <v>1.638280384340694</v>
       </c>
       <c r="N159" t="n">
-        <v>-1.227948204151452</v>
+        <v>4.057533421276923</v>
       </c>
       <c r="O159" t="n">
-        <v>1.202153142138611</v>
+        <v>4.246966278760614</v>
       </c>
       <c r="P159" t="n">
-        <v>0.5709668045622129</v>
+        <v>2.242150044761781</v>
       </c>
       <c r="Q159" t="n">
-        <v>1.638280384340694</v>
+        <v>4.969360260113723</v>
       </c>
     </row>
     <row r="160">
@@ -9231,16 +9231,16 @@
         <v>0.8623003115263929</v>
       </c>
       <c r="N160" t="n">
-        <v>-0.8692198523402371</v>
+        <v>3.084538883273649</v>
       </c>
       <c r="O160" t="n">
-        <v>0.2170535478347227</v>
+        <v>1.985467678226337</v>
       </c>
       <c r="P160" t="n">
-        <v>0.8015490523529814</v>
+        <v>3.700611811797102</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.8623003115263929</v>
+        <v>2.921892852031956</v>
       </c>
     </row>
     <row r="161">
@@ -9286,16 +9286,16 @@
         <v>1.138581342418515</v>
       </c>
       <c r="N161" t="n">
-        <v>0.2487619486310662</v>
+        <v>2.369888122460611</v>
       </c>
       <c r="O161" t="n">
-        <v>0.7809390559357163</v>
+        <v>3.75392717505768</v>
       </c>
       <c r="P161" t="n">
-        <v>1.961382762818593</v>
+        <v>6.566181953664825</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.138581342418515</v>
+        <v>3.910288508125532</v>
       </c>
     </row>
     <row r="162">
@@ -9341,16 +9341,16 @@
         <v>2.211148702535477</v>
       </c>
       <c r="N162" t="n">
-        <v>-0.5224631693566119</v>
+        <v>2.236716127069</v>
       </c>
       <c r="O162" t="n">
-        <v>-0.1706345140612807</v>
+        <v>1.845840023976476</v>
       </c>
       <c r="P162" t="n">
-        <v>1.492907204146833</v>
+        <v>4.731231983505974</v>
       </c>
       <c r="Q162" t="n">
-        <v>2.211148702535477</v>
+        <v>7.59866076113813</v>
       </c>
     </row>
     <row r="163">
@@ -9396,16 +9396,16 @@
         <v>0.387987973196392</v>
       </c>
       <c r="N163" t="n">
-        <v>0.2813919111918191</v>
+        <v>2.35616955878099</v>
       </c>
       <c r="O163" t="n">
-        <v>1.298384754327224</v>
+        <v>5.300380886426593</v>
       </c>
       <c r="P163" t="n">
-        <v>1.774849810485571</v>
+        <v>5.88696620637118</v>
       </c>
       <c r="Q163" t="n">
-        <v>0.387987973196392</v>
+        <v>1.874886363926555</v>
       </c>
     </row>
     <row r="164">
@@ -9451,16 +9451,16 @@
         <v>0.4671763995005609</v>
       </c>
       <c r="N164" t="n">
-        <v>0.2886320035754535</v>
+        <v>2.362769684835691</v>
       </c>
       <c r="O164" t="n">
-        <v>1.510714077043496</v>
+        <v>5.532561702577289</v>
       </c>
       <c r="P164" t="n">
-        <v>1.825722927387061</v>
+        <v>6.019095899926238</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.4671763995005609</v>
+        <v>1.847916492260252</v>
       </c>
     </row>
     <row r="165">
@@ -9506,16 +9506,16 @@
         <v>1.107604959550475</v>
       </c>
       <c r="N165" t="n">
-        <v>-0.710053020225093</v>
+        <v>2.028847635582799</v>
       </c>
       <c r="O165" t="n">
-        <v>1.116182422415145</v>
+        <v>3.199726551516814</v>
       </c>
       <c r="P165" t="n">
-        <v>1.16074270661773</v>
+        <v>3.480955562989176</v>
       </c>
       <c r="Q165" t="n">
-        <v>1.107604959550475</v>
+        <v>4.308083709425625</v>
       </c>
     </row>
     <row r="166">
@@ -9561,16 +9561,16 @@
         <v>1.06023268915034</v>
       </c>
       <c r="N166" t="n">
-        <v>-0.710053020225093</v>
+        <v>2.028847635582799</v>
       </c>
       <c r="O166" t="n">
-        <v>1.101742498615977</v>
+        <v>3.146513399891867</v>
       </c>
       <c r="P166" t="n">
-        <v>1.136860207947171</v>
+        <v>3.37274671165395</v>
       </c>
       <c r="Q166" t="n">
-        <v>1.06023268915034</v>
+        <v>4.022699228951133</v>
       </c>
     </row>
     <row r="167">
@@ -9616,16 +9616,16 @@
         <v>1.160698203992283</v>
       </c>
       <c r="N167" t="n">
-        <v>-0.7089801683672796</v>
+        <v>1.999133290257367</v>
       </c>
       <c r="O167" t="n">
-        <v>1.155789468971408</v>
+        <v>3.689560035194154</v>
       </c>
       <c r="P167" t="n">
-        <v>1.300906657382509</v>
+        <v>4.208150784183514</v>
       </c>
       <c r="Q167" t="n">
-        <v>1.160698203992283</v>
+        <v>4.492583202790417</v>
       </c>
     </row>
     <row r="168">
@@ -9671,16 +9671,16 @@
         <v>1.093367807476319</v>
       </c>
       <c r="N168" t="n">
-        <v>-0.584060998655294</v>
+        <v>2.392039886341436</v>
       </c>
       <c r="O168" t="n">
-        <v>0.3383397870532448</v>
+        <v>2.303634682210069</v>
       </c>
       <c r="P168" t="n">
-        <v>0.3192957027134053</v>
+        <v>2.244341805724509</v>
       </c>
       <c r="Q168" t="n">
-        <v>1.093367807476319</v>
+        <v>4.713906589878637</v>
       </c>
     </row>
     <row r="169">
@@ -9726,16 +9726,16 @@
         <v>0.8007905178625696</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.4579284027697064</v>
+        <v>2.159357192220662</v>
       </c>
       <c r="O169" t="n">
-        <v>1.723465197447517</v>
+        <v>5.791043897724947</v>
       </c>
       <c r="P169" t="n">
-        <v>1.990123297972938</v>
+        <v>6.88385617009853</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.8007905178625696</v>
+        <v>2.898885886749526</v>
       </c>
     </row>
     <row r="170">
@@ -9781,16 +9781,16 @@
         <v>1.364224661992742</v>
       </c>
       <c r="N170" t="n">
-        <v>0.1560421849868494</v>
+        <v>2.504030485333855</v>
       </c>
       <c r="O170" t="n">
-        <v>-0.1405830046031425</v>
+        <v>1.448262490006183</v>
       </c>
       <c r="P170" t="n">
-        <v>0.7175960747493488</v>
+        <v>2.678084057980903</v>
       </c>
       <c r="Q170" t="n">
-        <v>1.364224661992742</v>
+        <v>5.025267890531491</v>
       </c>
     </row>
     <row r="171">
@@ -9836,16 +9836,16 @@
         <v>1.295538339386402</v>
       </c>
       <c r="N171" t="n">
-        <v>-0.7733839651471071</v>
+        <v>3.761647934721427</v>
       </c>
       <c r="O171" t="n">
-        <v>1.106045288468881</v>
+        <v>3.002649621562541</v>
       </c>
       <c r="P171" t="n">
-        <v>2.036744752984815</v>
+        <v>6.838217744722537</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.295538339386402</v>
+        <v>3.556658239380413</v>
       </c>
     </row>
     <row r="172">
@@ -9891,16 +9891,16 @@
         <v>0.4169335989877698</v>
       </c>
       <c r="N172" t="n">
-        <v>-0.2013709188536451</v>
+        <v>2.192714059158764</v>
       </c>
       <c r="O172" t="n">
-        <v>1.308893438940027</v>
+        <v>3.999860895952147</v>
       </c>
       <c r="P172" t="n">
-        <v>1.428697155338586</v>
+        <v>4.649124071180053</v>
       </c>
       <c r="Q172" t="n">
-        <v>0.4169335989877698</v>
+        <v>2.213515681122209</v>
       </c>
     </row>
     <row r="173">
@@ -9946,16 +9946,16 @@
         <v>0.5724403073175188</v>
       </c>
       <c r="N173" t="n">
-        <v>-0.2040251747367005</v>
+        <v>2.178278229881243</v>
       </c>
       <c r="O173" t="n">
-        <v>1.171019061199305</v>
+        <v>3.648529168840151</v>
       </c>
       <c r="P173" t="n">
-        <v>1.243221252011494</v>
+        <v>4.084140649752699</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.5724403073175188</v>
+        <v>2.261719105812165</v>
       </c>
     </row>
     <row r="174">
@@ -10001,16 +10001,16 @@
         <v>0.796084456760501</v>
       </c>
       <c r="N174" t="n">
-        <v>-0.2170856368128402</v>
+        <v>2.22730478790051</v>
       </c>
       <c r="O174" t="n">
-        <v>0.6154537434567103</v>
+        <v>2.619036532675542</v>
       </c>
       <c r="P174" t="n">
-        <v>0.7236090326922199</v>
+        <v>2.555984034103428</v>
       </c>
       <c r="Q174" t="n">
-        <v>0.796084456760501</v>
+        <v>3.197968951060606</v>
       </c>
     </row>
     <row r="175">
@@ -10056,16 +10056,16 @@
         <v>0.9003459881541519</v>
       </c>
       <c r="N175" t="n">
-        <v>-1.078404601672351</v>
+        <v>3.553170399729034</v>
       </c>
       <c r="O175" t="n">
-        <v>-0.2313760235842982</v>
+        <v>1.749522038341957</v>
       </c>
       <c r="P175" t="n">
-        <v>0.1204049196442503</v>
+        <v>1.779543669716583</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.9003459881541519</v>
+        <v>3.109081755268581</v>
       </c>
     </row>
     <row r="176">
@@ -10111,16 +10111,16 @@
         <v>1.133980069219378</v>
       </c>
       <c r="N176" t="n">
-        <v>-1.074578004164006</v>
+        <v>3.61593686071435</v>
       </c>
       <c r="O176" t="n">
-        <v>-0.2263560523240052</v>
+        <v>1.84619583555377</v>
       </c>
       <c r="P176" t="n">
-        <v>0.1618824271842217</v>
+        <v>1.675579737664047</v>
       </c>
       <c r="Q176" t="n">
-        <v>1.133980069219378</v>
+        <v>3.793209141673714</v>
       </c>
     </row>
     <row r="177">
@@ -10166,16 +10166,16 @@
         <v>1.01781623306028</v>
       </c>
       <c r="N177" t="n">
-        <v>-1.17160586273961</v>
+        <v>3.766523984346233</v>
       </c>
       <c r="O177" t="n">
-        <v>-0.1910272622511228</v>
+        <v>1.648687412502978</v>
       </c>
       <c r="P177" t="n">
-        <v>0.09217560242764389</v>
+        <v>1.701961209568008</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.01781623306028</v>
+        <v>3.457509770053214</v>
       </c>
     </row>
     <row r="178">
@@ -10221,16 +10221,16 @@
         <v>-0.1346020138946836</v>
       </c>
       <c r="N178" t="n">
-        <v>-0.5774941064928379</v>
+        <v>2.178436357010013</v>
       </c>
       <c r="O178" t="n">
-        <v>1.174089738511835</v>
+        <v>3.478684891221168</v>
       </c>
       <c r="P178" t="n">
-        <v>1.386781222718841</v>
+        <v>4.112421302012451</v>
       </c>
       <c r="Q178" t="n">
-        <v>-0.1346020138946836</v>
+        <v>1.676072621787607</v>
       </c>
     </row>
     <row r="179">
@@ -10276,16 +10276,16 @@
         <v>-0.09140634725162804</v>
       </c>
       <c r="N179" t="n">
-        <v>-0.5488937091076438</v>
+        <v>2.165547644396693</v>
       </c>
       <c r="O179" t="n">
-        <v>0.96407678880443</v>
+        <v>3.13417700980827</v>
       </c>
       <c r="P179" t="n">
-        <v>1.215668795725308</v>
+        <v>3.683100388395011</v>
       </c>
       <c r="Q179" t="n">
-        <v>-0.09140634725162804</v>
+        <v>1.957444929152212</v>
       </c>
     </row>
     <row r="180">
@@ -10331,16 +10331,16 @@
         <v>-0.01369983858718697</v>
       </c>
       <c r="N180" t="n">
-        <v>-0.5561102281444028</v>
+        <v>2.174385631365195</v>
       </c>
       <c r="O180" t="n">
-        <v>0.9634210220500087</v>
+        <v>3.042231021756358</v>
       </c>
       <c r="P180" t="n">
-        <v>1.236981201508359</v>
+        <v>3.722561525851583</v>
       </c>
       <c r="Q180" t="n">
-        <v>-0.01369983858718697</v>
+        <v>2.005307063938679</v>
       </c>
     </row>
     <row r="181">
@@ -10386,16 +10386,16 @@
         <v>-0.03285224836367227</v>
       </c>
       <c r="N181" t="n">
-        <v>-0.5561102281444028</v>
+        <v>2.174385631365195</v>
       </c>
       <c r="O181" t="n">
-        <v>0.9679035522537942</v>
+        <v>3.04871440191247</v>
       </c>
       <c r="P181" t="n">
-        <v>1.252567058128368</v>
+        <v>3.788443694808598</v>
       </c>
       <c r="Q181" t="n">
-        <v>-0.03285224836367227</v>
+        <v>2.111701992698601</v>
       </c>
     </row>
     <row r="182">
@@ -10441,16 +10441,16 @@
         <v>0.4381893385619874</v>
       </c>
       <c r="N182" t="n">
-        <v>-0.7832402582796728</v>
+        <v>3.27707196655687</v>
       </c>
       <c r="O182" t="n">
-        <v>-0.2877500287227394</v>
+        <v>1.615800701379462</v>
       </c>
       <c r="P182" t="n">
-        <v>0.1310774997273131</v>
+        <v>2.156189739769253</v>
       </c>
       <c r="Q182" t="n">
-        <v>0.4381893385619874</v>
+        <v>1.805019610574612</v>
       </c>
     </row>
     <row r="183">
@@ -10496,16 +10496,16 @@
         <v>1.354344902896661</v>
       </c>
       <c r="N183" t="n">
-        <v>-0.4673253763492686</v>
+        <v>2.071522132801701</v>
       </c>
       <c r="O183" t="n">
-        <v>1.436623400480595</v>
+        <v>5.426063960071858</v>
       </c>
       <c r="P183" t="n">
-        <v>1.132396316605081</v>
+        <v>4.277843722896951</v>
       </c>
       <c r="Q183" t="n">
-        <v>1.354344902896661</v>
+        <v>4.629942617968287</v>
       </c>
     </row>
     <row r="184">
@@ -10551,16 +10551,16 @@
         <v>0.78605565878933</v>
       </c>
       <c r="N184" t="n">
-        <v>-0.8570345773176202</v>
+        <v>3.26262816877861</v>
       </c>
       <c r="O184" t="n">
-        <v>1.13897295195749</v>
+        <v>3.391366694355776</v>
       </c>
       <c r="P184" t="n">
-        <v>1.391122865076308</v>
+        <v>4.372147047766846</v>
       </c>
       <c r="Q184" t="n">
-        <v>0.78605565878933</v>
+        <v>2.201918372528311</v>
       </c>
     </row>
     <row r="185">
@@ -10606,16 +10606,16 @@
         <v>0.7927252538075428</v>
       </c>
       <c r="N185" t="n">
-        <v>0.01879004944215114</v>
+        <v>1.682575035275277</v>
       </c>
       <c r="O185" t="n">
-        <v>0.7526091234665981</v>
+        <v>2.728304568861655</v>
       </c>
       <c r="P185" t="n">
-        <v>0.08787292885442634</v>
+        <v>1.903895238088913</v>
       </c>
       <c r="Q185" t="n">
-        <v>0.7927252538075428</v>
+        <v>2.468691539047925</v>
       </c>
     </row>
     <row r="186">
@@ -10661,16 +10661,16 @@
         <v>0.4545292352489714</v>
       </c>
       <c r="N186" t="n">
-        <v>-0.6947846274353061</v>
+        <v>2.525337573573418</v>
       </c>
       <c r="O186" t="n">
-        <v>0.9563432072306087</v>
+        <v>3.560180762103587</v>
       </c>
       <c r="P186" t="n">
-        <v>1.226953986297077</v>
+        <v>4.670137000008875</v>
       </c>
       <c r="Q186" t="n">
-        <v>0.4545292352489714</v>
+        <v>2.010019540944768</v>
       </c>
     </row>
     <row r="187">
@@ -10716,16 +10716,16 @@
         <v>0.2378975897831767</v>
       </c>
       <c r="N187" t="n">
-        <v>-0.6933291078283927</v>
+        <v>2.543673376448945</v>
       </c>
       <c r="O187" t="n">
-        <v>1.010834298952612</v>
+        <v>3.721043065420764</v>
       </c>
       <c r="P187" t="n">
-        <v>1.109562864940381</v>
+        <v>4.325438361419385</v>
       </c>
       <c r="Q187" t="n">
-        <v>0.2378975897831767</v>
+        <v>2.043966496494054</v>
       </c>
     </row>
     <row r="188">
@@ -10771,16 +10771,16 @@
         <v>0.3018497756981957</v>
       </c>
       <c r="N188" t="n">
-        <v>-0.6933291078283927</v>
+        <v>2.543673376448945</v>
       </c>
       <c r="O188" t="n">
-        <v>0.8813816660894945</v>
+        <v>3.326156144043082</v>
       </c>
       <c r="P188" t="n">
-        <v>1.060284942690767</v>
+        <v>4.136906502871967</v>
       </c>
       <c r="Q188" t="n">
-        <v>0.3018497756981957</v>
+        <v>1.92474668474468</v>
       </c>
     </row>
     <row r="189">
@@ -10826,16 +10826,16 @@
         <v>0.7737230543747026</v>
       </c>
       <c r="N189" t="n">
-        <v>-0.6933291078283927</v>
+        <v>2.543673376448945</v>
       </c>
       <c r="O189" t="n">
-        <v>0.9633477578223116</v>
+        <v>3.526426446946884</v>
       </c>
       <c r="P189" t="n">
-        <v>1.217352692935065</v>
+        <v>4.589365747351219</v>
       </c>
       <c r="Q189" t="n">
-        <v>0.7737230543747026</v>
+        <v>2.444539474111722</v>
       </c>
     </row>
     <row r="190">
@@ -10881,16 +10881,16 @@
         <v>0.2528731804650102</v>
       </c>
       <c r="N190" t="n">
-        <v>-1.398155793724363</v>
+        <v>4.613010936511908</v>
       </c>
       <c r="O190" t="n">
-        <v>1.04256380766371</v>
+        <v>3.633058560244399</v>
       </c>
       <c r="P190" t="n">
-        <v>0.9450676818840028</v>
+        <v>3.080716463207736</v>
       </c>
       <c r="Q190" t="n">
-        <v>0.2528731804650102</v>
+        <v>2.100780001771017</v>
       </c>
     </row>
     <row r="191">
@@ -10936,16 +10936,16 @@
         <v>1.444090625939217</v>
       </c>
       <c r="N191" t="n">
-        <v>-0.5346931935703056</v>
+        <v>2.26835190265151</v>
       </c>
       <c r="O191" t="n">
-        <v>-0.03677688243700351</v>
+        <v>1.734574623973271</v>
       </c>
       <c r="P191" t="n">
-        <v>0.5171544719752671</v>
+        <v>2.177177140407696</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.444090625939217</v>
+        <v>5.033518810885017</v>
       </c>
     </row>
     <row r="192">
@@ -10991,16 +10991,16 @@
         <v>1.178130742690363</v>
       </c>
       <c r="N192" t="n">
-        <v>-0.5389911762727913</v>
+        <v>2.297884128109462</v>
       </c>
       <c r="O192" t="n">
-        <v>0.1293427510349051</v>
+        <v>1.841544274687505</v>
       </c>
       <c r="P192" t="n">
-        <v>0.4428017762828724</v>
+        <v>1.864328619255876</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.178130742690363</v>
+        <v>4.242533557016007</v>
       </c>
     </row>
     <row r="193">
@@ -11046,16 +11046,16 @@
         <v>0.323456182427581</v>
       </c>
       <c r="N193" t="n">
-        <v>-0.4777497856722427</v>
+        <v>2.983117209189545</v>
       </c>
       <c r="O193" t="n">
-        <v>0.774890762047745</v>
+        <v>2.831230414020521</v>
       </c>
       <c r="P193" t="n">
-        <v>0.26853172007236</v>
+        <v>2.335934651591549</v>
       </c>
       <c r="Q193" t="n">
-        <v>0.323456182427581</v>
+        <v>2.48044359035441</v>
       </c>
     </row>
     <row r="194">
@@ -11101,16 +11101,16 @@
         <v>-0.2638612308540407</v>
       </c>
       <c r="N194" t="n">
-        <v>-0.1116645967712445</v>
+        <v>4.237025604804599</v>
       </c>
       <c r="O194" t="n">
-        <v>0.6645667434482609</v>
+        <v>2.288576092806222</v>
       </c>
       <c r="P194" t="n">
-        <v>0.9411231780935985</v>
+        <v>2.698221016566077</v>
       </c>
       <c r="Q194" t="n">
-        <v>-0.2638612308540407</v>
+        <v>1.537732173344927</v>
       </c>
     </row>
     <row r="195">
@@ -11156,16 +11156,16 @@
         <v>0.3516085302077686</v>
       </c>
       <c r="N195" t="n">
-        <v>0.5216558475468975</v>
+        <v>2.412292803802988</v>
       </c>
       <c r="O195" t="n">
-        <v>1.118999763055717</v>
+        <v>3.007923367612434</v>
       </c>
       <c r="P195" t="n">
-        <v>1.223796280307992</v>
+        <v>3.139655191502718</v>
       </c>
       <c r="Q195" t="n">
-        <v>0.3516085302077686</v>
+        <v>1.774557237985524</v>
       </c>
     </row>
     <row r="196">
@@ -11211,16 +11211,16 @@
         <v>1.076716405073199</v>
       </c>
       <c r="N196" t="n">
-        <v>0.2531859488055372</v>
+        <v>2.015805935731124</v>
       </c>
       <c r="O196" t="n">
-        <v>1.263547140874462</v>
+        <v>3.753316186225656</v>
       </c>
       <c r="P196" t="n">
-        <v>1.292964851954542</v>
+        <v>3.465557832177236</v>
       </c>
       <c r="Q196" t="n">
-        <v>1.076716405073199</v>
+        <v>3.268556802661233</v>
       </c>
     </row>
     <row r="197">
@@ -11266,16 +11266,16 @@
         <v>1.392798624650794</v>
       </c>
       <c r="N197" t="n">
-        <v>-1.308593158765242</v>
+        <v>4.42454773829227</v>
       </c>
       <c r="O197" t="n">
-        <v>0.4202295115892675</v>
+        <v>1.757762915955714</v>
       </c>
       <c r="P197" t="n">
-        <v>0.654368297742819</v>
+        <v>2.466725162526382</v>
       </c>
       <c r="Q197" t="n">
-        <v>1.392798624650794</v>
+        <v>4.561673170237302</v>
       </c>
     </row>
     <row r="198">
@@ -11321,16 +11321,16 @@
         <v>-0.8137658575032057</v>
       </c>
       <c r="N198" t="n">
-        <v>-0.9689411816555413</v>
+        <v>3.37003468069957</v>
       </c>
       <c r="O198" t="n">
-        <v>-0.268363306994727</v>
+        <v>2.095340872403324</v>
       </c>
       <c r="P198" t="n">
-        <v>-0.3882363595282275</v>
+        <v>1.894104436096587</v>
       </c>
       <c r="Q198" t="n">
-        <v>-0.8137658575032057</v>
+        <v>2.671212176702258</v>
       </c>
     </row>
     <row r="199">
@@ -11376,16 +11376,16 @@
         <v>0.02130753587338879</v>
       </c>
       <c r="N199" t="n">
-        <v>-0.006760954409917199</v>
+        <v>2.457194733061771</v>
       </c>
       <c r="O199" t="n">
-        <v>-0.2321985135247132</v>
+        <v>1.830076541988879</v>
       </c>
       <c r="P199" t="n">
-        <v>0.4159377511551719</v>
+        <v>1.776897336444374</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.02130753587338879</v>
+        <v>1.866549175654891</v>
       </c>
     </row>
     <row r="200">
@@ -11431,16 +11431,16 @@
         <v>0.4448288642693264</v>
       </c>
       <c r="N200" t="n">
-        <v>-0.809752332303083</v>
+        <v>2.693842658644005</v>
       </c>
       <c r="O200" t="n">
-        <v>-0.1272162703832673</v>
+        <v>1.716861844792</v>
       </c>
       <c r="P200" t="n">
-        <v>-0.2316939025465427</v>
+        <v>1.585865054011029</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.4448288642693264</v>
+        <v>2.172007097694322</v>
       </c>
     </row>
     <row r="201">
@@ -11486,16 +11486,16 @@
         <v>1.376328459787092</v>
       </c>
       <c r="N201" t="n">
-        <v>-0.4875595796265233</v>
+        <v>2.998081349721565</v>
       </c>
       <c r="O201" t="n">
-        <v>1.432111405274814</v>
+        <v>4.987752121484935</v>
       </c>
       <c r="P201" t="n">
-        <v>0.9001337782787815</v>
+        <v>3.320030648656675</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.376328459787092</v>
+        <v>4.855746703277421</v>
       </c>
     </row>
     <row r="202">
@@ -11541,16 +11541,16 @@
         <v>0.7576069758013371</v>
       </c>
       <c r="N202" t="n">
-        <v>-0.9844750215795979</v>
+        <v>3.439841231550663</v>
       </c>
       <c r="O202" t="n">
-        <v>0.5418111813351704</v>
+        <v>2.450437816860403</v>
       </c>
       <c r="P202" t="n">
-        <v>1.079817587056185</v>
+        <v>3.539728409817676</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.7576069758013371</v>
+        <v>3.472088232732853</v>
       </c>
     </row>
     <row r="203">
@@ -11596,16 +11596,16 @@
         <v>0.9812721738608668</v>
       </c>
       <c r="N203" t="n">
-        <v>0.2552456384836939</v>
+        <v>2.037659057548975</v>
       </c>
       <c r="O203" t="n">
-        <v>0.7710186214627849</v>
+        <v>1.947699150685465</v>
       </c>
       <c r="P203" t="n">
-        <v>0.8751235393063153</v>
+        <v>2.211870150973118</v>
       </c>
       <c r="Q203" t="n">
-        <v>0.9812721738608668</v>
+        <v>3.678564956531821</v>
       </c>
     </row>
     <row r="204">
@@ -11651,16 +11651,16 @@
         <v>2.582670122048282</v>
       </c>
       <c r="N204" t="n">
-        <v>-0.7532109990175969</v>
+        <v>2.977158387840533</v>
       </c>
       <c r="O204" t="n">
-        <v>0.5644040335967547</v>
+        <v>2.259495275847381</v>
       </c>
       <c r="P204" t="n">
-        <v>0.6051776995080151</v>
+        <v>2.690230708427857</v>
       </c>
       <c r="Q204" t="n">
-        <v>2.582670122048282</v>
+        <v>8.941272927599288</v>
       </c>
     </row>
     <row r="205">
@@ -11706,16 +11706,16 @@
         <v>0.1559073067809648</v>
       </c>
       <c r="N205" t="n">
-        <v>-0.1115652953302766</v>
+        <v>1.80959639574998</v>
       </c>
       <c r="O205" t="n">
-        <v>-0.1084208200088821</v>
+        <v>1.48445417875458</v>
       </c>
       <c r="P205" t="n">
-        <v>0.2476010352236196</v>
+        <v>1.991869189577063</v>
       </c>
       <c r="Q205" t="n">
-        <v>0.1559073067809648</v>
+        <v>2.267029278999233</v>
       </c>
     </row>
     <row r="206">
@@ -11761,16 +11761,16 @@
         <v>0.01646814650752883</v>
       </c>
       <c r="N206" t="n">
-        <v>-0.438305758237705</v>
+        <v>2.137406254111662</v>
       </c>
       <c r="O206" t="n">
-        <v>0.2536666651804163</v>
+        <v>1.75372269101474</v>
       </c>
       <c r="P206" t="n">
-        <v>0.6081999196979234</v>
+        <v>2.375654139359526</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.01646814650752883</v>
+        <v>1.886719929657217</v>
       </c>
     </row>
     <row r="207">
@@ -11816,16 +11816,16 @@
         <v>0.2392058345542269</v>
       </c>
       <c r="N207" t="n">
-        <v>-0.4495159376808262</v>
+        <v>2.136210650435945</v>
       </c>
       <c r="O207" t="n">
-        <v>0.2842353110196241</v>
+        <v>1.74307015606643</v>
       </c>
       <c r="P207" t="n">
-        <v>0.6251134626884166</v>
+        <v>2.395373271815087</v>
       </c>
       <c r="Q207" t="n">
-        <v>0.2392058345542269</v>
+        <v>1.887471021897211</v>
       </c>
     </row>
     <row r="208">
@@ -11871,16 +11871,16 @@
         <v>0.9746341286308405</v>
       </c>
       <c r="N208" t="n">
-        <v>-1.130959037818492</v>
+        <v>3.700370138570856</v>
       </c>
       <c r="O208" t="n">
-        <v>1.292760906403372</v>
+        <v>4.309945960980553</v>
       </c>
       <c r="P208" t="n">
-        <v>1.134347619724245</v>
+        <v>4.10388577154309</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.9746341286308405</v>
+        <v>2.657560525009647</v>
       </c>
     </row>
     <row r="209">
@@ -11926,16 +11926,16 @@
         <v>0.2079262654610465</v>
       </c>
       <c r="N209" t="n">
-        <v>-0.02307441738415823</v>
+        <v>1.887324819229973</v>
       </c>
       <c r="O209" t="n">
-        <v>-0.04426407698968145</v>
+        <v>1.79920049708037</v>
       </c>
       <c r="P209" t="n">
-        <v>-0.4020376301304278</v>
+        <v>1.947240046051746</v>
       </c>
       <c r="Q209" t="n">
-        <v>0.2079262654610465</v>
+        <v>2.472800492620248</v>
       </c>
     </row>
     <row r="210">
@@ -11981,16 +11981,16 @@
         <v>-0.4485429668646427</v>
       </c>
       <c r="N210" t="n">
-        <v>-0.6487230721608646</v>
+        <v>3.203370889017151</v>
       </c>
       <c r="O210" t="n">
-        <v>0.6773910654439432</v>
+        <v>2.434272239330595</v>
       </c>
       <c r="P210" t="n">
-        <v>0.4115387987250653</v>
+        <v>1.861545316242665</v>
       </c>
       <c r="Q210" t="n">
-        <v>-0.4485429668646427</v>
+        <v>3.34834928240293</v>
       </c>
     </row>
     <row r="211">
@@ -12036,16 +12036,16 @@
         <v>0.4952738819472847</v>
       </c>
       <c r="N211" t="n">
-        <v>-0.8773502604247804</v>
+        <v>3.217487174176808</v>
       </c>
       <c r="O211" t="n">
-        <v>1.109755841006047</v>
+        <v>4.29138687858507</v>
       </c>
       <c r="P211" t="n">
-        <v>1.579583370027033</v>
+        <v>5.711423097230828</v>
       </c>
       <c r="Q211" t="n">
-        <v>0.4952738819472847</v>
+        <v>3.046763728730005</v>
       </c>
     </row>
     <row r="212">
@@ -12091,16 +12091,16 @@
         <v>0.2562433500022677</v>
       </c>
       <c r="N212" t="n">
-        <v>-0.0290999872039009</v>
+        <v>1.940115761819396</v>
       </c>
       <c r="O212" t="n">
-        <v>0.05310850239658661</v>
+        <v>2.377278564430035</v>
       </c>
       <c r="P212" t="n">
-        <v>0.2129546987085468</v>
+        <v>1.509510966352009</v>
       </c>
       <c r="Q212" t="n">
-        <v>0.2562433500022677</v>
+        <v>1.872351099498089</v>
       </c>
     </row>
     <row r="213">
@@ -12146,16 +12146,16 @@
         <v>0.3920770707543812</v>
       </c>
       <c r="N213" t="n">
-        <v>-0.05480667286304159</v>
+        <v>1.988372384915047</v>
       </c>
       <c r="O213" t="n">
-        <v>0.2277297295651903</v>
+        <v>2.475375796242579</v>
       </c>
       <c r="P213" t="n">
-        <v>0.2165277477716806</v>
+        <v>1.646180112158046</v>
       </c>
       <c r="Q213" t="n">
-        <v>0.3920770707543812</v>
+        <v>2.245168867382922</v>
       </c>
     </row>
     <row r="214">
@@ -12201,16 +12201,16 @@
         <v>-0.4409584085241194</v>
       </c>
       <c r="N214" t="n">
-        <v>-0.7365505349242703</v>
+        <v>1.985092705492191</v>
       </c>
       <c r="O214" t="n">
-        <v>0.6004853564953783</v>
+        <v>1.86540726078617</v>
       </c>
       <c r="P214" t="n">
-        <v>0.4133766756730308</v>
+        <v>1.636261105122646</v>
       </c>
       <c r="Q214" t="n">
-        <v>-0.4409584085241194</v>
+        <v>3.296603004808141</v>
       </c>
     </row>
     <row r="215">
@@ -12256,16 +12256,16 @@
         <v>0.737318826915604</v>
       </c>
       <c r="N215" t="n">
-        <v>-0.6804856946170749</v>
+        <v>2.737994950481065</v>
       </c>
       <c r="O215" t="n">
-        <v>-0.4088440991961081</v>
+        <v>2.228590715466205</v>
       </c>
       <c r="P215" t="n">
-        <v>0.5724141731514335</v>
+        <v>3.608698981127095</v>
       </c>
       <c r="Q215" t="n">
-        <v>0.737318826915604</v>
+        <v>2.979009448410435</v>
       </c>
     </row>
     <row r="216">
@@ -12311,16 +12311,16 @@
         <v>-0.123135391145297</v>
       </c>
       <c r="N216" t="n">
-        <v>-0.2435270054094838</v>
+        <v>3.209130836119839</v>
       </c>
       <c r="O216" t="n">
-        <v>-0.4416986309878588</v>
+        <v>2.08438323414982</v>
       </c>
       <c r="P216" t="n">
-        <v>-0.3835594897521341</v>
+        <v>2.127377048518795</v>
       </c>
       <c r="Q216" t="n">
-        <v>-0.123135391145297</v>
+        <v>1.722514324221784</v>
       </c>
     </row>
     <row r="217">
@@ -12366,16 +12366,16 @@
         <v>-0.1734051768345041</v>
       </c>
       <c r="N217" t="n">
-        <v>-0.2439317971241707</v>
+        <v>3.240255103459779</v>
       </c>
       <c r="O217" t="n">
-        <v>-0.4575614371912396</v>
+        <v>2.224594109497566</v>
       </c>
       <c r="P217" t="n">
-        <v>-0.3628472063293504</v>
+        <v>2.172276716882925</v>
       </c>
       <c r="Q217" t="n">
-        <v>-0.1734051768345041</v>
+        <v>1.712037336909584</v>
       </c>
     </row>
     <row r="218">
@@ -12421,16 +12421,16 @@
         <v>1.035347195052532</v>
       </c>
       <c r="N218" t="n">
-        <v>-2.342497900767511</v>
+        <v>7.802238755500544</v>
       </c>
       <c r="O218" t="n">
-        <v>1.139734239486508</v>
+        <v>4.015377033050035</v>
       </c>
       <c r="P218" t="n">
-        <v>1.432737688845598</v>
+        <v>5.289592699641109</v>
       </c>
       <c r="Q218" t="n">
-        <v>1.035347195052532</v>
+        <v>3.922770515463246</v>
       </c>
     </row>
     <row r="219">
@@ -12476,16 +12476,16 @@
         <v>1.178042864827473</v>
       </c>
       <c r="N219" t="n">
-        <v>-2.342497900767511</v>
+        <v>7.802238755500544</v>
       </c>
       <c r="O219" t="n">
-        <v>1.11955935710679</v>
+        <v>3.857396436011621</v>
       </c>
       <c r="P219" t="n">
-        <v>1.434315095380588</v>
+        <v>5.27878432325511</v>
       </c>
       <c r="Q219" t="n">
-        <v>1.178042864827473</v>
+        <v>4.487352617719069</v>
       </c>
     </row>
     <row r="220">
@@ -12531,16 +12531,16 @@
         <v>1.030055550124191</v>
       </c>
       <c r="N220" t="n">
-        <v>-0.2178036887707388</v>
+        <v>2.26000279532147</v>
       </c>
       <c r="O220" t="n">
-        <v>1.470075668162417</v>
+        <v>4.144446286533223</v>
       </c>
       <c r="P220" t="n">
-        <v>1.230466128862335</v>
+        <v>3.203791199019909</v>
       </c>
       <c r="Q220" t="n">
-        <v>1.030055550124191</v>
+        <v>3.001014774766106</v>
       </c>
     </row>
     <row r="221">
@@ -12586,16 +12586,16 @@
         <v>0.9336807136659192</v>
       </c>
       <c r="N221" t="n">
-        <v>-0.2178036887707388</v>
+        <v>2.26000279532147</v>
       </c>
       <c r="O221" t="n">
-        <v>0.7410716059836965</v>
+        <v>2.215878023046171</v>
       </c>
       <c r="P221" t="n">
-        <v>1.038181363359194</v>
+        <v>3.294626353691273</v>
       </c>
       <c r="Q221" t="n">
-        <v>0.9336807136659192</v>
+        <v>2.570918993679648</v>
       </c>
     </row>
     <row r="222">
@@ -12641,16 +12641,16 @@
         <v>-0.008442064529183344</v>
       </c>
       <c r="N222" t="n">
-        <v>0.09812988428686327</v>
+        <v>1.988781054947731</v>
       </c>
       <c r="O222" t="n">
-        <v>0.4320101302400225</v>
+        <v>2.329936901995684</v>
       </c>
       <c r="P222" t="n">
-        <v>0.118124604649296</v>
+        <v>1.8801182665479</v>
       </c>
       <c r="Q222" t="n">
-        <v>-0.008442064529183344</v>
+        <v>2.166083769605398</v>
       </c>
     </row>
     <row r="223">
@@ -12696,16 +12696,16 @@
         <v>0.1804720228936665</v>
       </c>
       <c r="N223" t="n">
-        <v>-0.6635033167558309</v>
+        <v>2.967574631935234</v>
       </c>
       <c r="O223" t="n">
-        <v>0.683426534546363</v>
+        <v>1.979736985242324</v>
       </c>
       <c r="P223" t="n">
-        <v>0.5679342681169662</v>
+        <v>1.969667961947546</v>
       </c>
       <c r="Q223" t="n">
-        <v>0.1804720228936665</v>
+        <v>2.274442349420403</v>
       </c>
     </row>
     <row r="224">
@@ -12751,16 +12751,16 @@
         <v>-0.006748067696593293</v>
       </c>
       <c r="N224" t="n">
-        <v>0.2163392823392719</v>
+        <v>3.154497148582391</v>
       </c>
       <c r="O224" t="n">
-        <v>-0.2089452852945488</v>
+        <v>2.401186576206026</v>
       </c>
       <c r="P224" t="n">
-        <v>0.3741907901174817</v>
+        <v>3.319222729977503</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.006748067696593293</v>
+        <v>2.310153034432377</v>
       </c>
     </row>
     <row r="225">
@@ -12806,16 +12806,16 @@
         <v>0.749030966212652</v>
       </c>
       <c r="N225" t="n">
-        <v>-0.03957149772493824</v>
+        <v>1.4171911209378</v>
       </c>
       <c r="O225" t="n">
-        <v>-0.5856931269244693</v>
+        <v>2.477119129882777</v>
       </c>
       <c r="P225" t="n">
-        <v>0.8347651761548767</v>
+        <v>4.059680580284882</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.749030966212652</v>
+        <v>2.092130171343404</v>
       </c>
     </row>
     <row r="226">
@@ -12861,16 +12861,16 @@
         <v>0.641025644560525</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.4043091728857708</v>
+        <v>2.087125532451883</v>
       </c>
       <c r="O226" t="n">
-        <v>0.6507907460852927</v>
+        <v>2.73033916369666</v>
       </c>
       <c r="P226" t="n">
-        <v>0.4741102659351134</v>
+        <v>2.763542150115401</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.641025644560525</v>
+        <v>3.752201984122232</v>
       </c>
     </row>
     <row r="227">
@@ -12916,16 +12916,16 @@
         <v>0.5572698437256697</v>
       </c>
       <c r="N227" t="n">
-        <v>-0.4043091728857708</v>
+        <v>2.087125532451883</v>
       </c>
       <c r="O227" t="n">
-        <v>0.5599259803810634</v>
+        <v>2.600309238651179</v>
       </c>
       <c r="P227" t="n">
-        <v>0.4530723351608448</v>
+        <v>2.712435932092214</v>
       </c>
       <c r="Q227" t="n">
-        <v>0.5572698437256697</v>
+        <v>3.648489693308184</v>
       </c>
     </row>
     <row r="228">
@@ -12971,16 +12971,16 @@
         <v>-0.03780267129580323</v>
       </c>
       <c r="N228" t="n">
-        <v>0.1064534257053479</v>
+        <v>1.909208795629634</v>
       </c>
       <c r="O228" t="n">
-        <v>1.141926489148966</v>
+        <v>3.421706669132333</v>
       </c>
       <c r="P228" t="n">
-        <v>1.498885740407318</v>
+        <v>4.614402112126998</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.03780267129580323</v>
+        <v>1.986406929504629</v>
       </c>
     </row>
     <row r="229">
@@ -13026,16 +13026,16 @@
         <v>0.3372229418259293</v>
       </c>
       <c r="N229" t="n">
-        <v>1.613803803734062</v>
+        <v>5.981688833956102</v>
       </c>
       <c r="O229" t="n">
-        <v>0.1782325993814823</v>
+        <v>1.923524762079518</v>
       </c>
       <c r="P229" t="n">
-        <v>0.8204160803828108</v>
+        <v>3.148247652781361</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.3372229418259293</v>
+        <v>2.176651024729996</v>
       </c>
     </row>
     <row r="230">
@@ -13081,16 +13081,16 @@
         <v>0.7415552937790181</v>
       </c>
       <c r="N230" t="n">
-        <v>-0.4740494076771416</v>
+        <v>2.342421428925536</v>
       </c>
       <c r="O230" t="n">
-        <v>-0.2564615204526503</v>
+        <v>3.337908048230566</v>
       </c>
       <c r="P230" t="n">
-        <v>1.36330736487128</v>
+        <v>4.795728163282043</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.7415552937790181</v>
+        <v>2.937093898123278</v>
       </c>
     </row>
     <row r="231">
@@ -13136,16 +13136,16 @@
         <v>-0.7734948839449844</v>
       </c>
       <c r="N231" t="n">
-        <v>-1.635864704634191</v>
+        <v>4.535141285993668</v>
       </c>
       <c r="O231" t="n">
-        <v>1.019375571066546</v>
+        <v>4.077815345117615</v>
       </c>
       <c r="P231" t="n">
-        <v>0.6126612417534566</v>
+        <v>2.795305688908985</v>
       </c>
       <c r="Q231" t="n">
-        <v>-0.7734948839449844</v>
+        <v>4.848008074225659</v>
       </c>
     </row>
     <row r="232">
@@ -13191,16 +13191,16 @@
         <v>-0.9743044089053752</v>
       </c>
       <c r="N232" t="n">
-        <v>-1.634001268820304</v>
+        <v>4.529013277689358</v>
       </c>
       <c r="O232" t="n">
-        <v>0.743837056468906</v>
+        <v>3.53015068513055</v>
       </c>
       <c r="P232" t="n">
-        <v>0.4775153789641057</v>
+        <v>2.511953543945768</v>
       </c>
       <c r="Q232" t="n">
-        <v>-0.9743044089053752</v>
+        <v>5.142198418590975</v>
       </c>
     </row>
     <row r="233">
@@ -13246,16 +13246,16 @@
         <v>-0.6710010821604598</v>
       </c>
       <c r="N233" t="n">
-        <v>-1.634001268820304</v>
+        <v>4.529013277689358</v>
       </c>
       <c r="O233" t="n">
-        <v>0.9984135377315695</v>
+        <v>4.012113019960981</v>
       </c>
       <c r="P233" t="n">
-        <v>0.5830475071892244</v>
+        <v>2.782080947147201</v>
       </c>
       <c r="Q233" t="n">
-        <v>-0.6710010821604598</v>
+        <v>4.862672857443488</v>
       </c>
     </row>
     <row r="234">
@@ -13301,16 +13301,16 @@
         <v>-0.6328160075820232</v>
       </c>
       <c r="N234" t="n">
-        <v>-1.664048206267576</v>
+        <v>4.117446152476787</v>
       </c>
       <c r="O234" t="n">
-        <v>0.3252738784720142</v>
+        <v>2.301404403849841</v>
       </c>
       <c r="P234" t="n">
-        <v>0.6700540120676827</v>
+        <v>2.946717589579551</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.6328160075820232</v>
+        <v>2.859040072341884</v>
       </c>
     </row>
     <row r="235">
@@ -13356,16 +13356,16 @@
         <v>-0.1668290288020034</v>
       </c>
       <c r="N235" t="n">
-        <v>-1.152784562878935</v>
+        <v>3.767109470836193</v>
       </c>
       <c r="O235" t="n">
-        <v>0.4420343995337993</v>
+        <v>1.895108951776354</v>
       </c>
       <c r="P235" t="n">
-        <v>0.2717977692618754</v>
+        <v>2.101264672359942</v>
       </c>
       <c r="Q235" t="n">
-        <v>-0.1668290288020034</v>
+        <v>2.901683942752184</v>
       </c>
     </row>
     <row r="236">
@@ -13411,16 +13411,16 @@
         <v>-0.3638686899239345</v>
       </c>
       <c r="N236" t="n">
-        <v>-0.1318034001210815</v>
+        <v>2.07596147962945</v>
       </c>
       <c r="O236" t="n">
-        <v>0.5341141105485748</v>
+        <v>2.541596930918324</v>
       </c>
       <c r="P236" t="n">
-        <v>0.03964922799688193</v>
+        <v>1.653500063006923</v>
       </c>
       <c r="Q236" t="n">
-        <v>-0.3638686899239345</v>
+        <v>2.373088464584795</v>
       </c>
     </row>
     <row r="237">
@@ -13466,16 +13466,16 @@
         <v>0.733395067875183</v>
       </c>
       <c r="N237" t="n">
-        <v>-1.096416719732478</v>
+        <v>3.561480484393954</v>
       </c>
       <c r="O237" t="n">
-        <v>0.08581938124670828</v>
+        <v>1.682870572524171</v>
       </c>
       <c r="P237" t="n">
-        <v>0.3328495612558126</v>
+        <v>1.669816655252974</v>
       </c>
       <c r="Q237" t="n">
-        <v>0.733395067875183</v>
+        <v>2.259282721073852</v>
       </c>
     </row>
     <row r="238">
@@ -13521,16 +13521,16 @@
         <v>-0.5228314654163718</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.657370017699868</v>
+        <v>4.10499054999409</v>
       </c>
       <c r="O238" t="n">
-        <v>0.663600825907723</v>
+        <v>2.788165041486476</v>
       </c>
       <c r="P238" t="n">
-        <v>1.154829673757648</v>
+        <v>3.885239215676624</v>
       </c>
       <c r="Q238" t="n">
-        <v>-0.5228314654163718</v>
+        <v>2.109009500034702</v>
       </c>
     </row>
     <row r="239">
@@ -13576,16 +13576,16 @@
         <v>0.5320306140214062</v>
       </c>
       <c r="N239" t="n">
-        <v>0.5130553321858743</v>
+        <v>2.04673710230343</v>
       </c>
       <c r="O239" t="n">
-        <v>0.3315727932590347</v>
+        <v>2.216909686967544</v>
       </c>
       <c r="P239" t="n">
-        <v>0.6283475544558437</v>
+        <v>2.801633471688655</v>
       </c>
       <c r="Q239" t="n">
-        <v>0.5320306140214062</v>
+        <v>2.446042385008056</v>
       </c>
     </row>
     <row r="240">
@@ -13631,16 +13631,16 @@
         <v>-0.1409042033674368</v>
       </c>
       <c r="N240" t="n">
-        <v>0.9576991685331931</v>
+        <v>4.153138761508419</v>
       </c>
       <c r="O240" t="n">
-        <v>-0.2963921209478004</v>
+        <v>2.203132048398192</v>
       </c>
       <c r="P240" t="n">
-        <v>0.4987168813613249</v>
+        <v>2.326808658798861</v>
       </c>
       <c r="Q240" t="n">
-        <v>-0.1409042033674368</v>
+        <v>1.877677435384983</v>
       </c>
     </row>
     <row r="241">
@@ -13686,16 +13686,16 @@
         <v>1.542065616418688</v>
       </c>
       <c r="N241" t="n">
-        <v>0.02012429824550116</v>
+        <v>1.66916706029881</v>
       </c>
       <c r="O241" t="n">
-        <v>0.4329223858137998</v>
+        <v>1.971605112954329</v>
       </c>
       <c r="P241" t="n">
-        <v>0.5292889073246182</v>
+        <v>2.264670636570544</v>
       </c>
       <c r="Q241" t="n">
-        <v>1.542065616418688</v>
+        <v>5.948802542572991</v>
       </c>
     </row>
     <row r="242">
@@ -13741,16 +13741,16 @@
         <v>0.06250124479049077</v>
       </c>
       <c r="N242" t="n">
-        <v>-0.001270980477140829</v>
+        <v>1.609841977715227</v>
       </c>
       <c r="O242" t="n">
-        <v>0.2921922195163854</v>
+        <v>1.62658987217245</v>
       </c>
       <c r="P242" t="n">
-        <v>0.2497076704391167</v>
+        <v>1.814872644972927</v>
       </c>
       <c r="Q242" t="n">
-        <v>0.06250124479049077</v>
+        <v>3.177948266910184</v>
       </c>
     </row>
     <row r="243">
@@ -13796,16 +13796,16 @@
         <v>-0.3921999787011438</v>
       </c>
       <c r="N243" t="n">
-        <v>-1.655120443690463</v>
+        <v>4.096357779070186</v>
       </c>
       <c r="O243" t="n">
-        <v>0.455897564321626</v>
+        <v>2.32430095997056</v>
       </c>
       <c r="P243" t="n">
-        <v>0.2623083058105928</v>
+        <v>2.35802137159113</v>
       </c>
       <c r="Q243" t="n">
-        <v>-0.3921999787011438</v>
+        <v>2.335939530084397</v>
       </c>
     </row>
     <row r="244">
@@ -13851,16 +13851,16 @@
         <v>1.723911281194208</v>
       </c>
       <c r="N244" t="n">
-        <v>1.795526233252839</v>
+        <v>4.661741558253334</v>
       </c>
       <c r="O244" t="n">
-        <v>1.829917536240291</v>
+        <v>4.851946719422933</v>
       </c>
       <c r="P244" t="n">
-        <v>1.770711989598388</v>
+        <v>4.523946029466367</v>
       </c>
       <c r="Q244" t="n">
-        <v>1.723911281194208</v>
+        <v>4.262808884694635</v>
       </c>
     </row>
     <row r="245">
@@ -13906,16 +13906,16 @@
         <v>-0.2497360144497381</v>
       </c>
       <c r="N245" t="n">
-        <v>-1.597659832148432</v>
+        <v>5.26839128862034</v>
       </c>
       <c r="O245" t="n">
-        <v>0.6089559240754115</v>
+        <v>2.274377378390164</v>
       </c>
       <c r="P245" t="n">
-        <v>0.3649038095481675</v>
+        <v>2.006588713613352</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.2497360144497381</v>
+        <v>3.054057428244383</v>
       </c>
     </row>
     <row r="246">
@@ -13961,16 +13961,16 @@
         <v>-0.6094893671309043</v>
       </c>
       <c r="N246" t="n">
-        <v>-0.1215718388708428</v>
+        <v>2.327157129686502</v>
       </c>
       <c r="O246" t="n">
-        <v>0.7447297689764014</v>
+        <v>2.338420162062573</v>
       </c>
       <c r="P246" t="n">
-        <v>0.841679487045492</v>
+        <v>2.933494341441474</v>
       </c>
       <c r="Q246" t="n">
-        <v>-0.6094893671309043</v>
+        <v>2.953648866608885</v>
       </c>
     </row>
     <row r="247">
@@ -14016,16 +14016,16 @@
         <v>-0.3948299871961203</v>
       </c>
       <c r="N247" t="n">
-        <v>-0.1215718388708428</v>
+        <v>2.327157129686502</v>
       </c>
       <c r="O247" t="n">
-        <v>0.8454627678757687</v>
+        <v>2.544595341284317</v>
       </c>
       <c r="P247" t="n">
-        <v>0.9176757209589586</v>
+        <v>3.073810522567878</v>
       </c>
       <c r="Q247" t="n">
-        <v>-0.3948299871961203</v>
+        <v>2.524166728882759</v>
       </c>
     </row>
     <row r="248">
@@ -14071,16 +14071,16 @@
         <v>0.118221751328931</v>
       </c>
       <c r="N248" t="n">
-        <v>-0.1566068956546314</v>
+        <v>1.253159001041023</v>
       </c>
       <c r="O248" t="n">
-        <v>1.848572379080344</v>
+        <v>5.92662862385463</v>
       </c>
       <c r="P248" t="n">
-        <v>1.251296369317355</v>
+        <v>3.306361862572431</v>
       </c>
       <c r="Q248" t="n">
-        <v>0.118221751328931</v>
+        <v>1.536936184221087</v>
       </c>
     </row>
     <row r="249">
@@ -14126,16 +14126,16 @@
         <v>-0.1174967341895004</v>
       </c>
       <c r="N249" t="n">
-        <v>-1.571281225742883</v>
+        <v>4.010395085138931</v>
       </c>
       <c r="O249" t="n">
-        <v>-0.4747441269347784</v>
+        <v>2.143305640268727</v>
       </c>
       <c r="P249" t="n">
-        <v>-0.0964805113994254</v>
+        <v>2.083165518272845</v>
       </c>
       <c r="Q249" t="n">
-        <v>-0.1174967341895004</v>
+        <v>2.012659740829076</v>
       </c>
     </row>
     <row r="250">
@@ -14181,16 +14181,16 @@
         <v>0.8434545504530189</v>
       </c>
       <c r="N250" t="n">
-        <v>-0.3044035592971973</v>
+        <v>1.747894274639644</v>
       </c>
       <c r="O250" t="n">
-        <v>0.355161418979945</v>
+        <v>1.843587239729012</v>
       </c>
       <c r="P250" t="n">
-        <v>0.7136408781834028</v>
+        <v>2.196562470028045</v>
       </c>
       <c r="Q250" t="n">
-        <v>0.8434545504530189</v>
+        <v>2.616539662179828</v>
       </c>
     </row>
     <row r="251">
@@ -14236,16 +14236,16 @@
         <v>0.8003455059796968</v>
       </c>
       <c r="N251" t="n">
-        <v>-1.781477953489311</v>
+        <v>6.258764177319088</v>
       </c>
       <c r="O251" t="n">
-        <v>0.5684689845107842</v>
+        <v>2.126271678581329</v>
       </c>
       <c r="P251" t="n">
-        <v>0.1199785478505233</v>
+        <v>1.671833909304457</v>
       </c>
       <c r="Q251" t="n">
-        <v>0.8003455059796968</v>
+        <v>5.046408535046425</v>
       </c>
     </row>
     <row r="252">
@@ -14291,16 +14291,16 @@
         <v>0.7168460843337287</v>
       </c>
       <c r="N252" t="n">
-        <v>-0.4314751016972698</v>
+        <v>2.360706895048778</v>
       </c>
       <c r="O252" t="n">
-        <v>1.017325991452352</v>
+        <v>3.446653519308688</v>
       </c>
       <c r="P252" t="n">
-        <v>0.4216381247438389</v>
+        <v>1.878332398156431</v>
       </c>
       <c r="Q252" t="n">
-        <v>0.7168460843337287</v>
+        <v>2.452238431443045</v>
       </c>
     </row>
     <row r="253">
@@ -14346,16 +14346,16 @@
         <v>0.4926355824585806</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.906725661305306</v>
+        <v>6.627812818511905</v>
       </c>
       <c r="O253" t="n">
-        <v>0.9208318525120422</v>
+        <v>2.935467067879556</v>
       </c>
       <c r="P253" t="n">
-        <v>0.327109745090758</v>
+        <v>1.741688346808849</v>
       </c>
       <c r="Q253" t="n">
-        <v>0.4926355824585806</v>
+        <v>4.811152621061112</v>
       </c>
     </row>
     <row r="254">
@@ -14401,16 +14401,16 @@
         <v>0.541863787008471</v>
       </c>
       <c r="N254" t="n">
-        <v>-1.926845053361736</v>
+        <v>6.587879483248511</v>
       </c>
       <c r="O254" t="n">
-        <v>0.342789530067124</v>
+        <v>1.759367028061225</v>
       </c>
       <c r="P254" t="n">
-        <v>0.8424418860425394</v>
+        <v>3.100894542819358</v>
       </c>
       <c r="Q254" t="n">
-        <v>0.541863787008471</v>
+        <v>2.841953698770165</v>
       </c>
     </row>
     <row r="255">
@@ -14456,16 +14456,16 @@
         <v>0.4345806523663023</v>
       </c>
       <c r="N255" t="n">
-        <v>-0.8953687234644727</v>
+        <v>2.785939711534729</v>
       </c>
       <c r="O255" t="n">
-        <v>0.8015619045269805</v>
+        <v>3.282192326701947</v>
       </c>
       <c r="P255" t="n">
-        <v>0.4201082733577155</v>
+        <v>2.159711208740646</v>
       </c>
       <c r="Q255" t="n">
-        <v>0.4345806523663023</v>
+        <v>2.507731416611646</v>
       </c>
     </row>
     <row r="256">
@@ -14511,16 +14511,16 @@
         <v>0.4801533168558891</v>
       </c>
       <c r="N256" t="n">
-        <v>-0.8867819091228885</v>
+        <v>2.773446212921583</v>
       </c>
       <c r="O256" t="n">
-        <v>0.8112415764275198</v>
+        <v>3.26982088791399</v>
       </c>
       <c r="P256" t="n">
-        <v>0.4118497664045813</v>
+        <v>2.149232795051448</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.4801533168558891</v>
+        <v>2.404100495788675</v>
       </c>
     </row>
     <row r="257">
@@ -14566,16 +14566,16 @@
         <v>0.4538395724246254</v>
       </c>
       <c r="N257" t="n">
-        <v>-0.8780059685384484</v>
+        <v>2.760093353049228</v>
       </c>
       <c r="O257" t="n">
-        <v>0.8947170317059636</v>
+        <v>3.504524808898121</v>
       </c>
       <c r="P257" t="n">
-        <v>0.428008681554469</v>
+        <v>2.142186921526723</v>
       </c>
       <c r="Q257" t="n">
-        <v>0.4538395724246254</v>
+        <v>2.560216551466435</v>
       </c>
     </row>
     <row r="258">
@@ -14621,16 +14621,16 @@
         <v>-0.3841749233330786</v>
       </c>
       <c r="N258" t="n">
-        <v>-0.3407910406888349</v>
+        <v>2.218979132512557</v>
       </c>
       <c r="O258" t="n">
-        <v>0.5915538021592732</v>
+        <v>2.068209290906634</v>
       </c>
       <c r="P258" t="n">
-        <v>0.5550334440979601</v>
+        <v>2.114321200303892</v>
       </c>
       <c r="Q258" t="n">
-        <v>-0.3841749233330786</v>
+        <v>2.181639430992168</v>
       </c>
     </row>
     <row r="259">
@@ -14676,16 +14676,16 @@
         <v>-0.3055871247860067</v>
       </c>
       <c r="N259" t="n">
-        <v>-0.3407910406888349</v>
+        <v>2.218979132512557</v>
       </c>
       <c r="O259" t="n">
-        <v>0.6262810039736816</v>
+        <v>2.081162470499683</v>
       </c>
       <c r="P259" t="n">
-        <v>0.6193997694010558</v>
+        <v>2.125475176568553</v>
       </c>
       <c r="Q259" t="n">
-        <v>-0.3055871247860067</v>
+        <v>2.122589193708987</v>
       </c>
     </row>
     <row r="260">
@@ -14731,16 +14731,16 @@
         <v>1.517426214867898</v>
       </c>
       <c r="N260" t="n">
-        <v>-2.769474918436499</v>
+        <v>9.622351300595561</v>
       </c>
       <c r="O260" t="n">
-        <v>0.2122339844531217</v>
+        <v>1.913033414695732</v>
       </c>
       <c r="P260" t="n">
-        <v>1.174731079786431</v>
+        <v>3.243809274754584</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.517426214867898</v>
+        <v>4.828683119907772</v>
       </c>
     </row>
     <row r="261">
@@ -14786,16 +14786,16 @@
         <v>1.722016307701116</v>
       </c>
       <c r="N261" t="n">
-        <v>-2.769474918436499</v>
+        <v>9.622351300595561</v>
       </c>
       <c r="O261" t="n">
-        <v>0.4775279557331724</v>
+        <v>2.938810686584315</v>
       </c>
       <c r="P261" t="n">
-        <v>1.207900563561065</v>
+        <v>3.27435545743695</v>
       </c>
       <c r="Q261" t="n">
-        <v>1.722016307701116</v>
+        <v>5.556092804126249</v>
       </c>
     </row>
     <row r="262">
@@ -14841,16 +14841,16 @@
         <v>1.580124039812498</v>
       </c>
       <c r="N262" t="n">
-        <v>-2.769474918436499</v>
+        <v>9.622351300595561</v>
       </c>
       <c r="O262" t="n">
-        <v>0.4339536837706723</v>
+        <v>2.36581446311176</v>
       </c>
       <c r="P262" t="n">
-        <v>1.221461635054285</v>
+        <v>3.308823645253629</v>
       </c>
       <c r="Q262" t="n">
-        <v>1.580124039812498</v>
+        <v>5.101018915519204</v>
       </c>
     </row>
     <row r="263">
@@ -14896,16 +14896,16 @@
         <v>0.7908548547754544</v>
       </c>
       <c r="N263" t="n">
-        <v>-1.670031849112817</v>
+        <v>4.541564331065888</v>
       </c>
       <c r="O263" t="n">
-        <v>0.9821005301356461</v>
+        <v>3.00845819553529</v>
       </c>
       <c r="P263" t="n">
-        <v>0.7263635015678696</v>
+        <v>2.424871854334901</v>
       </c>
       <c r="Q263" t="n">
-        <v>0.7908548547754544</v>
+        <v>5.517087070450183</v>
       </c>
     </row>
     <row r="264">
@@ -14951,16 +14951,16 @@
         <v>-0.05869540489158104</v>
       </c>
       <c r="N264" t="n">
-        <v>-1.652645444040287</v>
+        <v>4.490903269174177</v>
       </c>
       <c r="O264" t="n">
-        <v>0.9816984084032542</v>
+        <v>4.114360118824136</v>
       </c>
       <c r="P264" t="n">
-        <v>0.265878782187315</v>
+        <v>2.035254340911405</v>
       </c>
       <c r="Q264" t="n">
-        <v>-0.05869540489158104</v>
+        <v>4.942441804502924</v>
       </c>
     </row>
     <row r="265">
@@ -15006,16 +15006,16 @@
         <v>-0.4887673091538784</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.652145788708926</v>
+        <v>4.49051680775408</v>
       </c>
       <c r="O265" t="n">
-        <v>0.7109768643018668</v>
+        <v>3.493701805074128</v>
       </c>
       <c r="P265" t="n">
-        <v>0.1083517801410554</v>
+        <v>1.793772080174232</v>
       </c>
       <c r="Q265" t="n">
-        <v>-0.4887673091538784</v>
+        <v>3.769058947452454</v>
       </c>
     </row>
     <row r="266">
@@ -15061,16 +15061,16 @@
         <v>1.22265957033424</v>
       </c>
       <c r="N266" t="n">
-        <v>-0.7620657763605112</v>
+        <v>2.798966262975787</v>
       </c>
       <c r="O266" t="n">
-        <v>0.6952034444909083</v>
+        <v>2.92745985491971</v>
       </c>
       <c r="P266" t="n">
-        <v>1.457069723429426</v>
+        <v>4.651057381787849</v>
       </c>
       <c r="Q266" t="n">
-        <v>1.22265957033424</v>
+        <v>3.206765946213457</v>
       </c>
     </row>
     <row r="267">
@@ -15116,16 +15116,16 @@
         <v>0.353589333400202</v>
       </c>
       <c r="N267" t="n">
-        <v>1.164170407731286</v>
+        <v>2.711568519049874</v>
       </c>
       <c r="O267" t="n">
-        <v>0.7762346428955921</v>
+        <v>2.229444667943353</v>
       </c>
       <c r="P267" t="n">
-        <v>1.261193677433215</v>
+        <v>3.94710014210089</v>
       </c>
       <c r="Q267" t="n">
-        <v>0.353589333400202</v>
+        <v>1.733603855349167</v>
       </c>
     </row>
     <row r="268">
@@ -15171,16 +15171,16 @@
         <v>0.3554623674168212</v>
       </c>
       <c r="N268" t="n">
-        <v>-1.502006812915852</v>
+        <v>4.27684500729641</v>
       </c>
       <c r="O268" t="n">
-        <v>0.8419103366539464</v>
+        <v>3.120713436385256</v>
       </c>
       <c r="P268" t="n">
-        <v>1.296187329496281</v>
+        <v>3.906919645584494</v>
       </c>
       <c r="Q268" t="n">
-        <v>0.3554623674168212</v>
+        <v>2.845442719195202</v>
       </c>
     </row>
     <row r="269">
@@ -15226,16 +15226,16 @@
         <v>1.552675689285314</v>
       </c>
       <c r="N269" t="n">
-        <v>-1.640905837930745</v>
+        <v>5.646728883628994</v>
       </c>
       <c r="O269" t="n">
-        <v>0.8471987675669018</v>
+        <v>2.633289670429256</v>
       </c>
       <c r="P269" t="n">
-        <v>0.5083069237085005</v>
+        <v>2.010544438292819</v>
       </c>
       <c r="Q269" t="n">
-        <v>1.552675689285314</v>
+        <v>5.594839901005423</v>
       </c>
     </row>
     <row r="270">
@@ -15281,16 +15281,16 @@
         <v>0.1483431363422512</v>
       </c>
       <c r="N270" t="n">
-        <v>0.5406003700496719</v>
+        <v>2.654015170697955</v>
       </c>
       <c r="O270" t="n">
-        <v>0.6291682455778559</v>
+        <v>2.362080094088415</v>
       </c>
       <c r="P270" t="n">
-        <v>0.5459008339332203</v>
+        <v>2.232959750635324</v>
       </c>
       <c r="Q270" t="n">
-        <v>0.1483431363422512</v>
+        <v>1.667210180846671</v>
       </c>
     </row>
     <row r="271">
@@ -15336,16 +15336,16 @@
         <v>1.108353924372503</v>
       </c>
       <c r="N271" t="n">
-        <v>-2.199232169308263</v>
+        <v>7.288863961476617</v>
       </c>
       <c r="O271" t="n">
-        <v>0.5734940059285049</v>
+        <v>3.128981955892181</v>
       </c>
       <c r="P271" t="n">
-        <v>0.08915141034578036</v>
+        <v>2.205283441079383</v>
       </c>
       <c r="Q271" t="n">
-        <v>1.108353924372503</v>
+        <v>4.412663696961005</v>
       </c>
     </row>
     <row r="272">
@@ -15391,16 +15391,16 @@
         <v>0.1963149626880704</v>
       </c>
       <c r="N272" t="n">
-        <v>0.5006958391845162</v>
+        <v>1.566116795433209</v>
       </c>
       <c r="O272" t="n">
-        <v>1.326253719153487</v>
+        <v>4.026261619368159</v>
       </c>
       <c r="P272" t="n">
-        <v>1.458818412820124</v>
+        <v>4.373435422857065</v>
       </c>
       <c r="Q272" t="n">
-        <v>0.1963149626880704</v>
+        <v>1.864983074890132</v>
       </c>
     </row>
     <row r="273">
@@ -15446,16 +15446,16 @@
         <v>0.1961990486881237</v>
       </c>
       <c r="N273" t="n">
-        <v>0.5007534137528745</v>
+        <v>1.570335243411498</v>
       </c>
       <c r="O273" t="n">
-        <v>1.284954458471748</v>
+        <v>3.980206527056625</v>
       </c>
       <c r="P273" t="n">
-        <v>1.487354742369237</v>
+        <v>4.549763506318407</v>
       </c>
       <c r="Q273" t="n">
-        <v>0.1961990486881237</v>
+        <v>1.833006213008052</v>
       </c>
     </row>
     <row r="274">
@@ -15501,16 +15501,16 @@
         <v>0.9618302107700646</v>
       </c>
       <c r="N274" t="n">
-        <v>0.7852093472100309</v>
+        <v>2.014731287955306</v>
       </c>
       <c r="O274" t="n">
-        <v>0.1890314763825399</v>
+        <v>1.455074139484531</v>
       </c>
       <c r="P274" t="n">
-        <v>0.5938447053439104</v>
+        <v>2.828999231836185</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.9618302107700646</v>
+        <v>4.607515990474694</v>
       </c>
     </row>
     <row r="275">
@@ -15556,16 +15556,16 @@
         <v>0.09040978722656774</v>
       </c>
       <c r="N275" t="n">
-        <v>0.5641348262683689</v>
+        <v>1.665998711013025</v>
       </c>
       <c r="O275" t="n">
-        <v>1.469569482206822</v>
+        <v>4.624811061291503</v>
       </c>
       <c r="P275" t="n">
-        <v>1.648816813027728</v>
+        <v>5.198323317252237</v>
       </c>
       <c r="Q275" t="n">
-        <v>0.09040978722656774</v>
+        <v>1.092293446189619</v>
       </c>
     </row>
     <row r="276">
@@ -15611,16 +15611,16 @@
         <v>0.08659814109050507</v>
       </c>
       <c r="N276" t="n">
-        <v>0.5641348262683689</v>
+        <v>1.665998711013025</v>
       </c>
       <c r="O276" t="n">
-        <v>1.41102193574039</v>
+        <v>4.350128074556793</v>
       </c>
       <c r="P276" t="n">
-        <v>1.564572640185477</v>
+        <v>4.790827801962489</v>
       </c>
       <c r="Q276" t="n">
-        <v>0.08659814109050507</v>
+        <v>1.094303977256703</v>
       </c>
     </row>
     <row r="277">
@@ -15666,16 +15666,16 @@
         <v>1.766240240075193</v>
       </c>
       <c r="N277" t="n">
-        <v>0.09791227214789831</v>
+        <v>3.508244741294408</v>
       </c>
       <c r="O277" t="n">
-        <v>0.5884231607528336</v>
+        <v>1.956836628511968</v>
       </c>
       <c r="P277" t="n">
-        <v>1.655860501109258</v>
+        <v>4.974233086006599</v>
       </c>
       <c r="Q277" t="n">
-        <v>1.766240240075193</v>
+        <v>5.783703864393048</v>
       </c>
     </row>
     <row r="278">
@@ -15721,16 +15721,16 @@
         <v>0.5211476824771962</v>
       </c>
       <c r="N278" t="n">
-        <v>1.263518119451671</v>
+        <v>3.189005749979696</v>
       </c>
       <c r="O278" t="n">
-        <v>1.388582451184434</v>
+        <v>3.789262436286785</v>
       </c>
       <c r="P278" t="n">
-        <v>1.466756843896305</v>
+        <v>4.111631303015708</v>
       </c>
       <c r="Q278" t="n">
-        <v>0.5211476824771962</v>
+        <v>2.095511802202525</v>
       </c>
     </row>
     <row r="279">
@@ -15776,16 +15776,16 @@
         <v>0.4031665847810496</v>
       </c>
       <c r="N279" t="n">
-        <v>-1.069224440456517</v>
+        <v>2.520555133147703</v>
       </c>
       <c r="O279" t="n">
-        <v>0.2686207574871107</v>
+        <v>2.26530612244898</v>
       </c>
       <c r="P279" t="n">
-        <v>0.2237216323760771</v>
+        <v>1.915898746074144</v>
       </c>
       <c r="Q279" t="n">
-        <v>0.4031665847810496</v>
+        <v>2.528457251126082</v>
       </c>
     </row>
     <row r="280">
@@ -15831,16 +15831,16 @@
         <v>2.02668352093038</v>
       </c>
       <c r="N280" t="n">
-        <v>1.756549500431475</v>
+        <v>4.445093706848042</v>
       </c>
       <c r="O280" t="n">
-        <v>2.263574391319671</v>
+        <v>7.165488041079231</v>
       </c>
       <c r="P280" t="n">
-        <v>2.626866631578641</v>
+        <v>8.952947673085378</v>
       </c>
       <c r="Q280" t="n">
-        <v>2.02668352093038</v>
+        <v>5.92210546997604</v>
       </c>
     </row>
     <row r="281">
@@ -15886,16 +15886,16 @@
         <v>0.1796179121206291</v>
       </c>
       <c r="N281" t="n">
-        <v>-1.295099706303273</v>
+        <v>3.283716848204556</v>
       </c>
       <c r="O281" t="n">
-        <v>1.528407025479517</v>
+        <v>5.219654087095874</v>
       </c>
       <c r="P281" t="n">
-        <v>0.8278143778282017</v>
+        <v>2.555278127705416</v>
       </c>
       <c r="Q281" t="n">
-        <v>0.1796179121206291</v>
+        <v>2.538381289851291</v>
       </c>
     </row>
     <row r="282">
@@ -15941,16 +15941,16 @@
         <v>0.4943179390021327</v>
       </c>
       <c r="N282" t="n">
-        <v>-1.295099706303273</v>
+        <v>3.283716848204556</v>
       </c>
       <c r="O282" t="n">
-        <v>1.499676686470172</v>
+        <v>5.142475325694376</v>
       </c>
       <c r="P282" t="n">
-        <v>0.7861196401147916</v>
+        <v>2.491214387029526</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.4943179390021327</v>
+        <v>3.010895758252349</v>
       </c>
     </row>
     <row r="283">
@@ -15996,16 +15996,16 @@
         <v>0.327592881853997</v>
       </c>
       <c r="N283" t="n">
-        <v>-1.30142087122078</v>
+        <v>3.294502379379918</v>
       </c>
       <c r="O283" t="n">
-        <v>1.403449276341525</v>
+        <v>4.709364781877722</v>
       </c>
       <c r="P283" t="n">
-        <v>0.7814933898629952</v>
+        <v>2.461551053090534</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.327592881853997</v>
+        <v>2.509003912034089</v>
       </c>
     </row>
     <row r="284">
@@ -16051,16 +16051,16 @@
         <v>1.494174272849299</v>
       </c>
       <c r="N284" t="n">
-        <v>1.914682520855111</v>
+        <v>5.496457177738566</v>
       </c>
       <c r="O284" t="n">
-        <v>1.607058109725267</v>
+        <v>4.012098373182649</v>
       </c>
       <c r="P284" t="n">
-        <v>1.692888037710162</v>
+        <v>4.258733860322357</v>
       </c>
       <c r="Q284" t="n">
-        <v>1.494174272849299</v>
+        <v>3.819722856954442</v>
       </c>
     </row>
     <row r="285">
@@ -16106,16 +16106,16 @@
         <v>2.886751094049554</v>
       </c>
       <c r="N285" t="n">
-        <v>2.886751345931585</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="O285" t="n">
-        <v>2.886751327557579</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="P285" t="n">
-        <v>2.886751345944192</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q285" t="n">
-        <v>2.886751094049554</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="286">
@@ -16161,16 +16161,16 @@
         <v>2.886751345230841</v>
       </c>
       <c r="N286" t="n">
-        <v>0.2633316162531078</v>
+        <v>1.222491945589998</v>
       </c>
       <c r="O286" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="P286" t="n">
-        <v>2.88675134585847</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q286" t="n">
-        <v>2.886751345230841</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="287">
@@ -16216,16 +16216,16 @@
         <v>2.886750787402782</v>
       </c>
       <c r="N287" t="n">
-        <v>2.886751345770123</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="O287" t="n">
-        <v>2.886748165458656</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="P287" t="n">
-        <v>2.88675134485722</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q287" t="n">
-        <v>2.886750787402782</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="288">
@@ -16271,16 +16271,16 @@
         <v>2.886750787402782</v>
       </c>
       <c r="N288" t="n">
-        <v>2.886751345770123</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="O288" t="n">
-        <v>2.886748165458656</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="P288" t="n">
-        <v>2.88675134485722</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q288" t="n">
-        <v>2.886750787402782</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="289">
@@ -16326,16 +16326,16 @@
         <v>1.038914372817633</v>
       </c>
       <c r="N289" t="n">
-        <v>0.03768395688029744</v>
+        <v>3.091005851618473</v>
       </c>
       <c r="O289" t="n">
-        <v>1.212656902040264</v>
+        <v>3.411950588911233</v>
       </c>
       <c r="P289" t="n">
-        <v>1.724484037484469</v>
+        <v>5.315770123656755</v>
       </c>
       <c r="Q289" t="n">
-        <v>1.038914372817633</v>
+        <v>2.624802673267566</v>
       </c>
     </row>
     <row r="290">
@@ -16381,16 +16381,16 @@
         <v>2.88675117365286</v>
       </c>
       <c r="N290" t="n">
-        <v>2.886751345230838</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="O290" t="n">
-        <v>2.886751335440735</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="P290" t="n">
-        <v>2.886751345946571</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q290" t="n">
-        <v>2.88675117365286</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="291">
@@ -16436,16 +16436,16 @@
         <v>2.886751277779128</v>
       </c>
       <c r="N291" t="n">
-        <v>2.886751344715095</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="O291" t="n">
-        <v>2.886734300594232</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="P291" t="n">
-        <v>2.886751345402777</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q291" t="n">
-        <v>2.886751277779128</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="292">
@@ -16491,16 +16491,16 @@
         <v>1.609186836288407</v>
       </c>
       <c r="N292" t="n">
-        <v>2.555036407551282</v>
+        <v>8.719933884297513</v>
       </c>
       <c r="O292" t="n">
-        <v>2.115831585250453</v>
+        <v>6.797886278277582</v>
       </c>
       <c r="P292" t="n">
-        <v>1.404958224751718</v>
+        <v>3.382437869822486</v>
       </c>
       <c r="Q292" t="n">
-        <v>1.609186836288407</v>
+        <v>4.528003874455155</v>
       </c>
     </row>
     <row r="293">
@@ -16546,7 +16546,7 @@
         <v>0</v>
       </c>
       <c r="N293" t="n">
-        <v>2.886614988752973</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -16601,7 +16601,7 @@
         <v>0</v>
       </c>
       <c r="N294" t="n">
-        <v>2.886614988752972</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -16656,7 +16656,7 @@
         <v>0</v>
       </c>
       <c r="N295" t="n">
-        <v>2.886614988752972</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -16711,7 +16711,7 @@
         <v>0</v>
       </c>
       <c r="N296" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -16766,16 +16766,16 @@
         <v>2.886747373594593</v>
       </c>
       <c r="N297" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O297" t="n">
-        <v>2.885660848958207</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="P297" t="n">
-        <v>2.886750849403339</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q297" t="n">
-        <v>2.886747373594593</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
     <row r="298">
@@ -16821,16 +16821,16 @@
         <v>2.886751344005336</v>
       </c>
       <c r="N298" t="n">
-        <v>2.885660848958208</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="O298" t="n">
-        <v>2.885660848958208</v>
+        <v>10.0909090909091</v>
       </c>
       <c r="P298" t="n">
-        <v>2.88675134570528</v>
+        <v>10.09090909090909</v>
       </c>
       <c r="Q298" t="n">
-        <v>2.886751344005336</v>
+        <v>10.09090909090909</v>
       </c>
     </row>
   </sheetData>
